--- a/untitled folder/HSC_Physics_2nd_Paper_Chapter_11_Astronomy.xlsx
+++ b/untitled folder/HSC_Physics_2nd_Paper_Chapter_11_Astronomy.xlsx
@@ -1219,11 +1219,6 @@
           <t>প্রমাণ করো যে কেপলারের দ্বিতীয় সূত্র (ক্ষেত্রফলের সূত্র) মূলত গ্রহের কৌণিক ভরবেগ সংরক্ষণ নীতির (Conservation of Angular Momentum) প্রত্যক্ষ প্রকাশ।</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>$dt$ সময়ে গ্রহের অবস্থান ভেক্টর $\vec{r}$ এবং সরণ $d\vec{r}$ হলে অতিক্রান্ত ক্ষেত্রফল $d\vec{A} = \frac{1}{2}(\vec{r} \times d\vec{r})$। ক্ষেত্রীয় বেগ $\frac{d\vec{A}}{dt} = \frac{1}{2}\left(\vec{r} \times \frac{d\vec{r}}{dt}\right) = \frac{1}{2}(\vec{r} \times \vec{v}) = \frac{\vec{L}}{2m}$। সূর্যের মহাকর্ষ বল একটি কেন্দ্রীয় বল (Central force), যার দিক সর্বদা ব্যাসার্ধ ভেক্টর বরাবর ($\vec{r} \parallel \vec{F}$)। ফলে টর্ক $\vec{\tau} = \vec{r} \times \vec{F} = 0$। টর্ক শূন্য হওয়ায় কৌণিক ভরবেগ $\vec{L}$ সর্বদা অপরিবর্তিত বা ধ্রুবক থাকে। ফলে ক্ষেত্রীয় বেগ $\frac{dA}{dt} = \frac{L}{2m} = \text{constant}$।</t>
@@ -1269,11 +1264,6 @@
           <t>একটি গ্রহের উপবৃত্তাকার কক্ষপথের উৎকেন্দ্রিকতা $e$। সূর্য থেকে নিকটতম দূরত্বে (অনুসূর বা Perihelion, $r_p$) এবং দূরতম দূরত্বে (অপসূর বা Aphelion, $r_a$) গ্রহটির দ্রুতির অনুপাত $v_p : v_a$ কত?</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>কৌণিক ভরবেগ সংরক্ষণ অনুযায়ী: $L = m v_p r_p = m v_a r_a \Rightarrow \frac{v_p}{v_a} = \frac{r_a}{r_p}$। উপবৃত্তের জ্যামিতি থেকে নিকটতম দূরত্ব $r_p = a(1 - e)$ এবং দূরতম দূরত্ব $r_a = a(1 + e)$। অতএব দ্রুতির অনুপাত: $\frac{v_p}{v_a} = \frac{a(1 + e)}{a(1 - e)} = \frac{1 + e}{1 - e}$। অনুসূর বিন্দুতে গ্রহ সূর্যের সবচেয়ে কাছে থাকে এবং সর্বাধিক দ্রুতিতে চলে; অপসূর বিন্দুতে সবচেয়ে দূরে থাকে এবং সর্বনিম্ন দ্রুতিতে চলে।</t>
@@ -1319,11 +1309,6 @@
           <t>স্যার আইজ্যাক নিউটন কেপলারের তৃতীয় সূত্রে উভয় বস্তুর ভর অন্তর্ভুক্ত করে যে সার্বজনীন সমীকরণ প্রতিপাদন করেন তা লেখো এবং সৌরজগতের বাইরে দ্বি-নাক্ষত্রিক জগতে এর গুরুত্ব কী?</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>নিউটনীয় সার্বজনীন রূপ: $T^2 = \frac{4\pi^2}{G(M_1 + M_2)} a^3$। সৌরজগতে সূর্যের ভর গ্রহগুলোর তুলনায় অতি বৃহৎ ($M_\odot \gg m_p$), ফলে $M_\odot + m_p \approx M_\odot$ ধরে কেপলারের সহজ সূত্র $T^2 \propto a^3$ ঠিক থাকে। কিন্তু বাইনারি স্টার (Binary Stars) বা পরস্পরের চারদিকে ঘূর্ণায়মান জোড়া নক্ষত্রের ক্ষেত্রে উভয়ের ভর সমতুল্য হওয়ায় নিউটনের এই সমীকরণ ব্যবহার করে নক্ষত্রদ্বয়ের কক্ষীয় পর্যায়কাল $T$ ও ব্যবধান $a$ পরিমাপের মাধ্যমে সরাসরি নক্ষত্রের সঠিক ভর ($M_1 + M_2$) নির্ণয় করা হয়।</t>
@@ -1369,11 +1354,6 @@
           <t>সূর্য থেকে একটি কাল্পনিক গ্রহের গড় দূরত্ব পৃথিবীর দূরত্বের ৪ গুণ ($a = 4\text{ AU}$)। কেপলারের তৃতীয় সূত্র অনুযায়ী গ্রহটির পর্যায়কাল কত পার্থিব বছর এবং এর কক্ষীয় বেগ পৃথিবীর কত গুণ?</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>কেপলারের সূত্রানুযায়ী $T^2 \propto a^3 \Rightarrow \left(\frac{T}{T_\oplus}\right)^2 = \left(\frac{a}{a_\oplus}\right)^3 = 4^3 = 64$। অতএব পর্যায়কাল $T = \sqrt{64} T_\oplus = 8\text{ বছর}$। বৃত্তাকার কক্ষীয় দ্রুতি $v = \sqrt{\frac{G M_\odot}{a}} \propto \frac{1}{\sqrt{a}}$। দূরত্ব ৪ গুণ হলে বেগ $\frac{v}{v_\oplus} = \frac{1}{\sqrt{4}} = \frac{1}{2} = 0.5$। অর্থাৎ গ্রহটি পৃথিবীর কক্ষীয় বেগের অর্ধেক বেগে চলে।</t>
@@ -1419,11 +1399,6 @@
           <t>$M$ ভরের নক্ষত্রকে কেন্দ্র করে $m$ ভরের একটি গ্রহ $a$ অর্ধ-মুখ্য অক্ষবিশিষ্ট উপবৃত্তাকার কক্ষপথে প্রদক্ষিণ করলে ব্যবস্থার মোট যান্ত্রিক শক্তি $E$-এর সমীকরণ কী এবং এটি কেবল $a$-এর ওপর নির্ভর করে কেন?</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>উপবৃত্তাকার কক্ষপথের জন্য মোট শক্তি $E = K + U = \frac{1}{2}m v^2 - \frac{G M m}{r}$। উপবৃত্তের যেকোনো বিন্দুতে ভিভা-ভিটা (Vis-viva) সমীকরণ: $v^2 = G M \left(\frac{2}{r} - \frac{1}{a}\right)$। মান বসালে: $E = \frac{1}{2}m G M \left(\frac{2}{r} - \frac{1}{a}\right) - \frac{G M m}{r} = \frac{G M m}{r} - \frac{G M m}{2a} - \frac{G M m}{r} = -\frac{G M m}{2a}$। চমৎকারভাবে দেখা যায় যে মোট শক্তি দূরত্বের ($r$) ওপর সম্পূর্ণ স্বাধীন এবং কেবল অর্ধ-মুখ্য অক্ষ $a$-এর ওপর নির্ভর করে।</t>
@@ -1469,11 +1444,6 @@
           <t>ভূপৃষ্ঠের অতি নিকটস্থ বৃত্তাকার কক্ষপথের উপগ্রহের বেগ $v_{\text{orb}}$ এবং মুক্তিবেগ $v_{\text{esc}}$-এর মধ্যে সম্পর্ক কী? কক্ষীয় গতিশীল উপগ্রহের গতিশক্তি কত শতাংশ বৃদ্ধি করলে এটি মহাকর্ষ কাটিয়ে মুক্ত হয়ে যাবে?</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>কক্ষীয় বেগ $v_{\text{orb}} = \sqrt{\frac{GM}{R}}$। মুক্তিবেগ $v_{\text{esc}} = \sqrt{\frac{2GM}{R}} = \sqrt{2} v_{\text{orb}} \approx 1.414 v_{\text{orb}}$। গতিশক্তি $K = \frac{1}{2}m v^2$। মুক্তি পাওয়ার জন্য প্রয়োজনীয় গতিশক্তি $K_{\text{esc}} = \frac{1}{2}m v_{\text{esc}}^2 = \frac{1}{2}m (2 v_{\text{orb}}^2) = 2 K_{\text{orb}}$। অর্থাৎ গতিশক্তি দ্বিগুণ (১০০% বৃদ্ধি) করতে হবে বা বেগকে প্রায় $41.4\%$ বৃদ্ধি করতে হবে।</t>
@@ -1517,11 +1487,6 @@
       <c r="G9" t="inlineStr">
         <is>
           <t>পৃথিবী থেকে মঙ্গল গ্রহে মহাকাশযান প্রেরণে ব্যবহৃত সর্বনিম্ন শক্তিসম্পন্ন 'হোহম্যান স্থানান্তর উপবৃত্তের' প্রধান অক্ষের দৈর্ঘ্য কত এবং এর অর্ধ-পর্যায়কাল কী নির্দেশ করে?</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1663,11 +1628,6 @@
           <t>জ্যোতির্বিজ্ঞানে ব্যবহৃত তিনটি মৌলিক দূরত্বের একক—জ্যোতির্বৈজ্ঞানিক একক (AU), আলোকবর্ষ (ly) এবং পারসেক (pc)-এর সুনির্দিষ্ট সংজ্ঞা ও মিটারে এদের মান লেখো।</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>(১) জ্যোতির্বৈজ্ঞানিক একক ($1\text{ AU}$): পৃথিবী থেকে সূর্যের গড় দূরত্ব; $1\text{ AU} = 1.496 \times 10^{11}\text{ m} \approx 1.5 \times 10^8\text{ km}$। (২) আলোকবর্ষ ($1\text{ ly}$): আলো শূন্য মাধ্যমে এক পার্থিব বছরে যে দূরত্ব অতিক্রম করে; $1\text{ ly} = c \times 365.25 \times 86400\text{ s} \approx 9.461 \times 10^{15}\text{ m} \approx 9.46 \times 10^{12}\text{ km}$। (৩) পারসেক ($1\text{ pc}$): Parallax of one arcsecond-এর সংক্ষিপ্ত রূপ; যে দূরত্বে $1\text{ AU}$ দৈর্ঘ্যের ভূমি ঠিক ১ আর্কমিনিট নয়, ১ আর্কেসেকেন্ড ($1''$) লম্বন কোণ তৈরি করে; $1\text{ pc} = \frac{1\text{ AU}}{1''} = \frac{1.496 \times 10^{11}\text{ m}}{\pi / (180 \times 3600)} \approx 3.086 \times 10^{16}\text{ m} \approx 3.26\text{ ly}$।</t>
@@ -1713,11 +1673,6 @@
           <t>নাক্ষত্রিক লম্বন (Stellar Parallax) পদ্ধতি কী? লম্বন কোণ $p$ (আর্কেসেকেন্ডে) হলে নক্ষত্রের দূরত্ব $d$ (পারসেকে)-এর সরাসরি সূত্রটি প্রতিপাদন করো।</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>সূর্যের চারদিকে পৃথিবীর বার্ষিক গতির কারণে ৬ মাসের ব্যবধানে দূরবর্তী স্থির পটভূমির সাপেক্ষে নিকটবর্তী কোনো নক্ষত্রের আপাত অবস্থানের যে কৌণিক পরিবর্তন ঘটে তার অর্ধেককে নাক্ষত্রিক লম্বন কোণ ($p$) বলে। ত্রিভুজমিতি অনুযায়ী $\tan p \approx p = \frac{1\text{ AU}}{d}$ (যেখানে $p$ রেডিয়ানে)। যদি $p$-কে আর্কেসেকেন্ডে ($''$) এবং $d$-কে পারসেকে প্রকাশ করা হয়, তবে পারসেকের সংজ্ঞানুযায়ী সরাসরি সমীকরণটি দাঁড়ায়: $d(\text{pc}) = \frac{1}{p('')}$। এটি জ্যামিতিক দূরত্বের সবচেয়ে নির্ভরযোগ্য প্রত্যক্ষ ভিত্তি।</t>
@@ -1763,11 +1718,6 @@
           <t>সৌরজগতের নিকটতম নক্ষত্র প্রক্সিমা সেন্টরাই (Proxima Centauri)-এর লম্বন কোণ $p = 0.768''$ হলে এর দূরত্ব কত পারসেক এবং কত আলোকবর্ষ?</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>পারসেকে দূরত্ব: $d = \frac{1}{p('')} = \frac{1}{0.768} \approx 1.302\text{ pc}$। আলোকবর্ষে দূরত্ব: যেহেতু $1\text{ pc} \approx 3.2616\text{ ly}$, সুতরাং $d = 1.302 \times 3.2616\text{ ly} \approx 4.246\text{ ly} \approx 4.25\text{ আলোকবর্ষ}$। অর্থাৎ আলো প্রক্সিমা সেন্টরাই থেকে পৃথিবীতে পৌঁছাতে ৪.২৫ বছর সময় নেয়।</t>
@@ -1813,11 +1763,6 @@
           <t>ভূপৃষ্ঠের সাধারণ দূরবীক্ষণ যন্ত্র দিয়ে কেন প্রায় ১০০ পারসেকের বেশি দূরের নক্ষত্রের লম্বন কোণ নির্ভুলভাবে মাপা যায় না? ইউরোপীয় মহাকাশ সংস্থার 'গাইয়া' (Gaia) মিশন কীভাবে এর সমাধান করেছে?</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>পৃথিবীর বায়ুমণ্ডলের অশান্ত তাপীয় প্রবাহের কারণে নাক্ষত্রিক আলো কাঁপতে থাকে (Atmospheric seeing), যার ফলে গ্রাউন্ড টেলিস্কোপে কৌণিক বিভেদন সীমা প্রায় $0.01''$-এ সীমাবদ্ধ থাকে। $d &gt; 100\text{ pc}$-এ লম্বন কোণ $p &lt; 0.01''$ হওয়ায় তা বায়ুমণ্ডলীয় বিভ্রান্তিতে হারিয়ে যায়। ২০১৩ সালে প্রেরিত মহাকাশ দূরবীক্ষণ 'গাইয়া' (Gaia) বায়ুমণ্ডলের বাইরে অবস্থান করে মাইক্রো-আর্কেসেকেন্ড ($\sim 10\ \mu\text{as}$) সূক্ষ্মতায় লম্বন পরিমাপ করে আমাদের গ্যালাক্সির প্রায় ১০০ কোটি নক্ষত্রের নির্ভুল ত্রিমাত্রিক দূরত্বের মানচিত্র তৈরি করেছে।</t>
@@ -1863,11 +1808,6 @@
           <t>মহাজাগতিক দূরত্বের সিঁড়ি (Cosmic Distance Ladder) বলতে কী বোঝায় এবং নিকট থেকে অতি দূরবর্তী গ্যালাক্সির দূরত্ব নির্ণয়ে ব্যবহৃত প্রধান তিনটি ধাপ কী কী?</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>মহাবিশ্বের কোনো একক পদ্ধতি দিয়ে সমস্ত দূরত্বের পরিমাপ সম্ভব নয়; নিকটবর্তী বস্তুর দূরত্ব মেপে তার সাহায্যে দূরবর্তী ধাপের ক্রমাঙ্কন (Calibration) করার ধারাবাহিক কৌশলকে মহাজাগতিক দূরত্বের সিঁড়ি বলে। তিনটি প্রধান ধাপ: (১) ত্রিকোণমিতিক লম্বন (Parallax): সৌরজগৎ ও নিকটবর্তী নক্ষত্রের জন্য ($&lt; 10\text{ kpc}$)। (২) শেফালী পরিবর্তনশীল তারা (Cepheid Variables): পর্যায়কাল-ঔজ্জ্বল্য সম্পর্কের মাধ্যমে নিকটবর্তী গ্যালাক্সির জন্য ($&lt; 30\text{ Mpc}$)। (৩) টাইপ Ia সুপারনোভা ও হাবলের সূত্র: প্রমাণ মোমবাতি হিসেবে বিলিয়ন আলোকবর্ষ দূরের প্রান্তীয় গ্যালাক্সির জন্য ($&gt; 1000\text{ Mpc}$)।</t>
@@ -1913,11 +1853,6 @@
           <t>১৯১২ সালে হেনরিয়েটা লিভিট (Henrietta Leavitt) আবিষ্কৃত শেফালী পরিবর্তনশীল তারার (Cepheid Variables) 'পর্যায়কাল-ঔজ্জ্বল্য সম্পর্ক' কীভাবে গ্যালাক্সির দূরত্ব নির্ণয়ে প্রমিত মোমবাতি (Standard Candle) হিসেবে কাজ করে?</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>লিভিট আবিষ্কার করেন যে শেফালী পরিবর্তনশীল নক্ষত্রের স্পন্দনের পর্যায়কাল ($P$) তার প্রকৃত অভ্যন্তরীণ মোট ঔজ্জ্বল্য বা পরম মানের ($M$) সাথে সরাসরি সম্পর্কিত: নক্ষত্র যত বেশি উজ্জ্বল, তার স্পন্দনকাল তত দীর্ঘ হয় ($M \propto -\log P$)। দূরবীক্ষণ দিয়ে নক্ষত্রটির পর্যায়কাল পরিমাপ করে এই সূত্র থেকে এর নিখুঁত পরম মান $M$ পাওয়া যায়। অতঃপর টেলিস্কোপে পর্যবেক্ষিত আপাত উজ্জ্বলতা $m$ পরিমাপ করে দূরত্বের মডিউলাস সমীকরণ ($m - M = 5\log d - 5$) প্রয়োগ করে নক্ষত্র ও সংশ্লিষ্ট গ্যালাক্সির সঠিক দূরত্ব $d$ নির্ণয় করা হয়। এডউইন হাবল এই পদ্ধতিতেই অ্যান্ড্রোমিডা গ্যালাক্সির দূরত্ব মেপেছিলেন।</t>
@@ -1963,11 +1898,6 @@
           <t>টাইপ Ia সুপারনোভাকে (Type Ia Supernovae) মহাবিশ্বের সুদূরতম প্রান্তের দূরত্ব নির্ণয়ে নিখুঁত 'প্রমাণ মোমবাতি' (Standard Candle) হিসেবে গণ্য করা হয় কেন?</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>টাইপ Ia সুপারনোভা ঘটে যখন একটি কার্বন-অক্সিজেন শ্বেত বামন নক্ষত্র তার সঙ্গী তারা থেকে ভর শোষণ করতে করতে ঠিক চন্দ্রশেখর ভরের সীমায় ($1.44 M_\odot$) পৌঁছায়। যেহেতু প্রতিটি বিস্ফোরণ ঠিক একই নির্দিষ্ট ভরে ($1.44 M_\odot$) থার্মোনিউক্লিয়ার বিস্ফোরণের মাধ্যমে ঘটে, তাই সমস্ত টাইপ Ia সুপারনোভার সর্বোচ্চ পিক ঔজ্জ্বল্য সর্বদা হুবহু একই এবং অত্যন্ত ধ্রুবক থাকে ($M_V \approx -19.3$)। এটি কোটি সূর্যের চেয়েও উজ্জ্বল হওয়ায় বিলিয়ন আলোকবর্ষ দূর থেকেও স্পষ্ট দৃশ্যমান হয় এবং এদের আপাত উজ্জ্বলতা মেপে মহাজাগতিক সম্প্রসারণের ত্বরণ (ডার্ক এনার্জি) আবিষ্কৃত হয়েছিল।</t>
@@ -2013,11 +1943,6 @@
           <t>সর্পিল গ্যালাক্সিগুলোর (Spiral Galaxies) ক্ষেত্রে টুলী-ফিশার সম্পর্কটি কী এবং এটি কীভাবে গ্যালাক্সির দূরত্ব নির্ণয়ে ব্যবহৃত হয়?</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>টুলী-ফিশার সম্পর্ক হলো একটি সর্পিল গ্যালাক্সির মোট অভ্যন্তরীণ ঔজ্জ্বল্য ($L$) এবং এর ঘূর্ণন গতির বিস্তারের (Rotational velocity width, $W$) মধ্যে গবেষণালব্ধ সম্পর্ক: $L \propto v_{\text{rot}}^4$। রেডিও টেলিস্কোপে ২১ সেমি হাইড্রোজেন রেখার ডপলার প্রসারণ থেকে গ্যালাক্সির ঘূর্ণন বেগ $v_{\text{rot}}$ নিখুঁতভাবে মাপা যায়। এই সম্পর্ক প্রয়োগ করে গ্যালাক্সিটির পরম ঔজ্জ্বল্য $L$ (বা $M$) নির্ধারণ করা হয় এবং পর্যবেক্ষিত আপাত উজ্জ্বলতার সাথে তুলনা করে গ্যালাক্সির দূরত্ব বের করা হয়।</t>
@@ -2063,11 +1988,6 @@
           <t>আধুনিক জ্যোতির্বিজ্ঞানে পৃথিবী থেকে শুক্র গ্রহে রাডার সংকেত পাঠিয়ে প্রতিফলিত সিগন্যালের সময় মেপে কীভাবে ১ জ্যোতির্বৈজ্ঞানিক একক ($1\text{ AU}$)-এর মান মিটারে অত্যন্ত নিখুঁতভাবে নির্ধারণ করা হয়েছে?</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>শুক্র গ্রহে প্রেরিত রাডার তরঙ্গের যাতায়াতের সময় $\Delta t$ পরিমাপ করে শুক্র ও পৃথিবীর তাৎক্ষণিক দূরত্ব নির্ণয় করা হয়: $d = \frac{c \Delta t}{2}$। কেপলারের সূত্র ও গ্রহীয় কক্ষপথের জ্যামিতিক মডেল থেকে শুক্র ও পৃথিবীর দূরত্বের সমীকরণকে জ্যোতির্বৈজ্ঞানিক এককে প্রকাশ করা যায়: $d = [a_\oplus - a_v(\theta)]\text{ AU}$। রাডারের প্রত্যক্ষ দূরত্বের সাথে তুলনা করে $1\text{ AU}$-এর মান মিটারে নির্ধারিত হয়: $1\text{ AU} = 149,597,870,700\text{ m}$ (মিটার স্তরের সূক্ষ্মতায় আন্তর্জাতিক মান)।</t>
@@ -2113,11 +2033,6 @@
           <t>পৃথিবী থেকে সূর্যের আপাত কৌণিক ব্যাস $\theta \approx 32'$ (আর্কমিনিট) এবং পৃথিবী-সূর্য দূরত্ব $1\text{ AU} \approx 1.5 \times 10^8\text{ km}$ হলে সূর্যের বাস্তব ব্যাস $D_\odot$ কত?</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>কৌণিক ব্যাসকে রেডিয়ানে রূপান্তর: $\theta = 32' = \frac{32}{60}^\circ = \frac{32 \times \pi}{60 \times 180}\text{ rad} \approx 9.308 \times 10^{-3}\text{ rad}$। সূর্যের ব্যাস $D_\odot = d \times \theta = (1.496 \times 10^8\text{ km}) \times (9.308 \times 10^{-3}) \approx 1.392 \times 10^6\text{ km} \approx 1.4 \times 10^6\text{ km}$। এটি পৃথিবীর ব্যাসের ($\sim 12,742\text{ km}$) প্রায় ১০৯ গুণ বড়।</t>
@@ -2163,11 +2078,6 @@
           <t>১৮৫৬ সালে নরম্যান পগসন প্রাচীন হিপ্পার্কাসের উজ্জ্বলতার স্কেলকে গাণিতিক রূপ দিয়ে যে সমীকরণ প্রণয়ন করেন (পগসনের সূত্র) তা লেখো এবং দুই নক্ষত্রের উজ্জ্বলতার অনুপাত ১০০ হলে তাদের আপাত মানের পার্থক্য কত?</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>পগসনের সূত্রানুযায়ী মানুষের চোখের অনুভূতি লোগারিদমিক সাড়া দেয়: $m_1 - m_2 = -2.5 \log_{10}\left(\frac{b_1}{b_2}\right)$ বা $\frac{b_1}{b_2} = 100^{(m_2 - m_1)/5} \approx 2.512^{(m_2 - m_1)}$। যদি দুটি নক্ষত্রের উজ্জ্বলতার অনুপাত $\frac{b_1}{b_2} = 100$ হয়, তবে তাদের মানের পার্থক্য: $m_2 - m_1 = 2.5 \log_{10}(100) = 2.5 \times 2 = 5$ মান। অর্থাৎ ৫ মানের পার্থক্য ঠিক ১০০ গুণ উজ্জ্বলতার পার্থক্যের সমতুল্য এবং প্রতি ১ মানের পার্থক্য $\sqrt[5]{100} \approx 2.512$ গুণ উজ্জ্বলতা নির্দেশ করে। মান যত কম (বা ঋণাত্মক), নক্ষত্র তত বেশি উজ্জ্বল।</t>
@@ -2213,11 +2123,6 @@
           <t>নক্ষত্রের পরম মান (Absolute Magnitude) $M$-এর আন্তর্জাতিক সংজ্ঞা কী এবং আপাত মান $m$, পরম মান $M$ এবং দূরত্বের ($d$, পারসেকে) মধ্যকার 'দূরত্ব মডিউলাস' সমীকরণটি প্রতিপাদন করো।</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>পরম মান হলো কোনো নক্ষত্রকে যদি পৃথিবী থেকে ঠিক ১০ পারসেক ($d_0 = 10\text{ pc}$) প্রমিত দূরত্বে রাখা হতো, তবে তার যে আপাত মান পরিলক্ষিত হতো। উজ্জ্বলতা দূরত্বের বর্গের ব্যস্তানুপাতিক: $\frac{b}{b_0} = \left(\frac{10}{d}\right)^2$। পগসনের সূত্রে বসালে: $m - M = -2.5 \log_{10}\left(\frac{10}{d}\right)^2 = -5 \log_{10}\left(\frac{10}{d}\right) = -5(\log_{10} 10 - \log_{10} d) = -5(1 - \log_{10} d) = 5\log_{10} d - 5$। রাশিমালা $(m - M)$-কে দূরত্বের মডিউলাস (Distance Modulus) বলা হয়।</t>
@@ -2263,11 +2168,6 @@
           <t>সূর্যের আপাত মান $m_\odot \approx -26.7$ এবং দূরত্ব $1\text{ AU} \approx 4.85 \times 10^{-6}\text{ pc}$। সূর্যের পরম মান $M_\odot$ কত এবং সাধারণ নক্ষত্রের তুলনায় সূর্যের উজ্জ্বলতার স্তর কেমন?</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>দূরত্ব মডিউলাস সূত্রে মান বসাই: $M = m - 5\log_{10} d + 5$। এখানে $m = -26.74$ এবং $d = \frac{1}{206265}\text{ pc} \approx 4.848 \times 10^{-6}\text{ pc}$। $\log_{10}(4.848 \times 10^{-6}) \approx -5.314$। ফলে $M_\odot = -26.74 - 5(-5.314) + 5 = -26.74 + 26.57 + 5 = +4.83 \approx +4.8$। অর্থাৎ সূর্যের পরম মান প্রায় $+4.8$, যা নির্দেশ করে সূর্যকে ১০ পারসেক দূরত্বে রাখলে আকাশে এটি একটি অতি সাধারণ ক্ষীণ খালি চোখে মাত্র দেখা যায় এমন মৃদু নক্ষত্র হিসেবে দেখা যেত।</t>
@@ -2313,11 +2213,6 @@
           <t>নক্ষত্রের মোট বিকিরণ ক্ষমতা বা ঔজ্জ্বল্য (Luminosity) $L$-এর সমীকরণটি নক্ষত্রের ব্যাসার্ধ $R$ এবং কার্যকর তাপমাত্রা $T_{\text{eff}}$-এর মাধ্যমে প্রকাশ করো এবং সূর্যের সাপেক্ষে সৌর এককে এর অনুপাত লেখো।</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>নক্ষত্রকে একটি গোলকাকার আদর্শ কৃষ্ণবস্তু বিবেচনা করলে এর মোট পৃষ্ঠের ক্ষেত্রফল $A = 4\pi R^2$। স্টিফান-বোল্টজম্যান সূত্রানুযায়ী নক্ষত্রের মোট নির্গত ক্ষমতা বা ঔজ্জ্বল্য: $L = 4\pi R^2 \sigma T_{\text{eff}}^4$। সূর্যের ঔজ্জ্বল্য $L_\odot = 4\pi R_\odot^2 \sigma T_\odot^4$ ($L_\odot \approx 3.828 \times 10^{26}\text{ W}$)। সৌর এককে কোনো নক্ষত্রের ঔজ্জ্বল্য: $\frac{L}{L_\odot} = \left(\frac{R}{R_\odot}\right)^2 \left(\frac{T_{\text{eff}}}{T_\odot}\right)^4$।</t>
@@ -2363,11 +2258,6 @@
           <t>একটি নক্ষত্রের আপাত মান $m = +12.0$ এবং এর পরম মান $M = +2.0$। নক্ষত্রটি পৃথিবী থেকে কত পারসেক এবং কত আলোকবর্ষ দূরে অবস্থিত?</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>দূরত্ব মডিউলাস সমীকরণ: $m - M = 5\log_{10} d - 5 \Rightarrow 12.0 - 2.0 = 5\log_{10} d - 5 \Rightarrow 10.0 = 5\log_{10} d - 5$। $5\log_{10} d = 15 \Rightarrow \log_{10} d = 3 \Rightarrow d = 10^3 = 1000\text{ pc}$। আলোকবর্ষে রূপান্তর: $d = 1000 \times 3.26\text{ ly} = 3260\text{ ly}$।</t>
@@ -2413,11 +2303,6 @@
           <t>রাতের আকাশের সবচেয়ে উজ্জ্বল নক্ষত্র লুব্ধক (Sirius A)-এর আপাত মান $m = -1.46$ এবং দূরত্ব $d = 2.64\text{ pc}$। এর পরম মান $M$ কত এবং এটি সূর্য অপেক্ষা কত গুণ বেশি আলো বিকিরণ করে?</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>পরম মান: $M = m - 5\log_{10} d + 5 = -1.46 - 5\log_{10}(2.64) + 5 = -1.46 - 5(0.4216) + 5 = -1.46 - 2.11 + 5 = +1.43$। সূর্যের পরম মান $M_\odot \approx +4.83$। মানের পার্থক্য: $M_\odot - M_{\text{Sirius}} = 4.83 - 1.43 = 3.40$। ঔজ্জ্বল্যের অনুপাত: $\frac{L}{L_\odot} = 100^{(M_\odot - M)/5} = 100^{3.40/5} = 100^{0.68} \approx 25.12^{0.68} \approx 25$ গুণ। অর্থাৎ সিরিয়াস সূর্য অপেক্ষা প্রায় ২৫ গুণ বেশি আলোকোজ্জ্বল।</t>
@@ -2463,11 +2348,6 @@
           <t>নক্ষত্রের 'বলোমেট্রিক মান' (Bolometric Magnitude - $M_{\text{bol}}$) বলতে কী বোঝায় এবং দৃশ্যমান আপাত মান থেকে এটি কেন ভিন্ন হয়?</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>সাধারণ অপটিক্যাল মান কেবল দৃশ্যমান বর্ণালীর আলো বিবেচনা করে। কিন্তু নক্ষত্র দৃশ্যমান আলোর পাশাপাশি প্রচুর অবলোহিত (IR) বা অতিবেগুনী (UV) বিকিরণ নির্গত করে। বলোমেট্রিক মান হলো নক্ষত্রের সমস্ত তরঙ্গদৈর্ঘ্যের (তড়িৎ-চৌম্বকীয় সম্পূর্ণ বর্ণালীর) মোট নিঃসৃত শক্তি পরিমাপক মান: $M_{\text{bol}} = M_V - BC$, যেখানে $BC$ হলো বলোমেট্রিক সংশোধন। অতি উত্তপ্ত নীল তারা (যা প্রধানত UV ছাড়ে) এবং অতি শীতল লাল তারা (যা প্রধানত IR ছাড়ে)-এর ক্ষেত্রে বলোমেট্রিক সংশোধন অত্যন্ত তাৎপর্যপূর্ণ হয়।</t>
@@ -2513,11 +2393,6 @@
           <t>আকাশে দুটি অতি নিকটবর্তী অপটিক্যাল নক্ষত্রের পৃথক আপাত মান যথাক্রমে $m_1 = 3.0$ এবং $m_2 = 3.0$। খালি চোখে তাদেরকে একটি একক নক্ষত্র হিসেবে দেখা গেলে তাদের সম্মিলিত আপাত মান কত হবে?</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>প্রতিটি নক্ষত্রের উজ্জ্বলতা সমান: $b_1 = b_2 = b$। সম্মিলিত উজ্জ্বলতা $b_{\text{total}} = b_1 + b_2 = 2b$। পগসনের সূত্রানুযায়ী: $m_{\text{total}} - m_1 = -2.5 \log_{10}\left(\frac{b_{\text{total}}}{b_1}\right) = -2.5 \log_{10}(2) = -2.5 \times 0.30103 \approx -0.75$। অতএব সম্মিলিত আপাত মান: $m_{\text{total}} = m_1 - 0.75 = 3.0 - 0.75 = 2.25$। অর্থাৎ দুটি ৩-মানের নক্ষত্র মিলে ২.২৫ মানের একটি উজ্জ্বলতর নক্ষত্র দেখাবে।</t>
@@ -2563,11 +2438,6 @@
           <t>জ্যোতির্বিজ্ঞানে নক্ষত্রের বর্ণ সূচক (Color Index) $B - V$ বলতে কী বোঝায় এবং একটি অতি উত্তপ্ত নীল নক্ষত্র ও একটি শীতল লাল নক্ষত্রের ক্ষেত্রে $B - V$-এর চিহ্ন কেমন হয়?</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>বর্ণ সূচক হলো নীল ফিল্টারে পরিমাপকৃত আপাত মান ($B$) এবং দৃশ্যমান হলুদ-সবুজ ফিল্টারে পরিমাপকৃত আপাত মানের ($V$) পার্থক্য: $CI = B - V$। এটি নক্ষত্রের তাপমাত্রার সরাসরি পরিমাপক। অতি উত্তপ্ত নীল নক্ষত্রে নীল আলোর তীব্রতা বেশি হওয়ায় $B$-মানের সংখ্যা কম (উজ্জ্বল) হয়, ফলে $B - V &lt; 0$ (ঋণাত্মক)। শীতল লাল নক্ষত্রে হলুদ ও লাল আলোর তীব্রতা বেশি হওয়ায় $V$ কম হয় কিন্তু $B$ বেশি হয়, ফলে $B - V &gt; 0$ (ধনাত্মক)। সূর্যের জন্য $B - V \approx +0.65$।</t>
@@ -2613,11 +2483,6 @@
           <t>প্রধান ধারার (Main Sequence) সাধারণ নক্ষত্রগুলোর জন্য ভর-ঔজ্জ্বল্য সম্পর্ক (Mass-Luminosity Relation) কী এবং সূর্যের দ্বিগুণ ভরের নক্ষত্রের ঔজ্জ্বল্য সূর্যের কত গুণ?</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>প্রধান ধারার নক্ষত্রগুলোর জন্য গবেষণালব্ধ ভর-ঔজ্জ্বল্য সম্পর্ক হলো: $L \propto M^\eta$, যেখানে মাঝারি ভরের নক্ষত্রের জন্য $\eta \approx 3.5$ (বা প্রায় $3$ থেকে $4$): $\frac{L}{L_\odot} \approx \left(\frac{M}{M_\odot}\right)^{3.5}$। সূর্যের দ্বিগুণ ভরের নক্ষত্রের জন্য ($M = 2 M_\odot$): $\frac{L}{L_\odot} \approx 2^{3.5} = 2^3 \times \sqrt{2} = 8 \times 1.414 \approx 11.3$ গুণ (বা $\eta=4$ ধরলে $2^4 = 16$ গুণ)। অর্থাৎ ভরের সামান্য বৃদ্ধিতেই নক্ষত্রের ঔজ্জ্বল্য ও জ্বালানি পোড়ানোর হার বিপুল পরিমাণে বৃদ্ধি পায়।</t>
@@ -2663,11 +2528,6 @@
           <t>হার্ভার্ড বর্ণালী শ্রেণীবিভাগের ক্রমটি (উষ্ণতম থেকে শীতলতম) লেখো এবং প্রতিটি শ্রেণীর সাধারণ বর্ণ ও আনুমানিক পৃষ্ঠ তাপমাত্রা উল্লেখ করো।</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>ক্রমটি মনে রাখার প্রচলিত সূত্র: 'Oh Be A Fine Girl/Guy, Kiss Me' (O, B, A, F, G, K, M)। (১) O: নীল, $T &gt; 30,000\text{ K}$ (আয়নিত হিলিয়াম রেখা)। (২) B: নীল-সাদা, $10,000 - 30,000\text{ K}$ (নিরপেক্ষ হিলিয়াম)। (৩) A: সাদা, $7,500 - 10,000\text{ K}$ (তীব্র হাইড্রোজেন বামার রেখা, উদা. ভেগা)। (৪) F: হলুদ-সাদা, $6,000 - 7,500\text{ K}$ (ধাতব ক্যালসিয়াম রেখা)। (৫) G: হলুদ, $5,200 - 6,000\text{ K}$ (সূর্য একটি G2V নক্ষত্র, $T \approx 5800\text{ K}$)। (৬) K: কমলা, $3,700 - 5,200\text{ K}$। (৭) M: লাল, $2,400 - 3,700\text{ K}$ (আণবিক TiO ব্যান্ড)।</t>
@@ -2713,11 +2573,6 @@
           <t>হার্টজস্প্রাং-রাসেল (H-R) ডায়াগ্রাম কী এবং এর উল্লম্ব অক্ষ (Y-axis) ও অনুভূমিক অক্ষে (X-axis) কোন কোন ভৌত রাশি স্থাপন করা হয়?</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>H-R ডায়াগাম হলো জ্যোতির্বিজ্ঞানের সবচেয়ে গুরুত্বপূর্ণ ডায়াগ্রাম যা নক্ষত্রদের শ্রেণীবদ্ধ করতে ও তাদের বিবর্তন বুঝতে ব্যবহৃত হয়। (১) উল্লম্ব অক্ষ (Y-axis): নক্ষত্রের ঔজ্জ্বল্য ($L/L_\odot$) অথবা পরম মান ($M$); নিচের দিকে ক্ষীণ এবং উপরের দিকে অতি উজ্জ্বল নক্ষত্র থাকে। (২) অনুভূমিক অক্ষ (X-axis): নক্ষত্রের কার্যকর পৃষ্ঠ তাপমাত্রা ($T$) অথবা বর্ণালী শ্রেণী (OBAFGKM) অথবা বর্ণ সূচক ($B-V$); প্রচলিত প্রথার বিপরীতভাবে এর তাপমাত্রা বাম থেকে ডানে হ্রাস পায় (বাম পাশে উষ্ণতম নীল তারা এবং ডান পাশে শীতলতম লাল তারা থাকে)।</t>
@@ -2763,11 +2618,6 @@
           <t>একটি সাধারণ H-R ডায়াগ্রামে নক্ষত্রদের চারটি প্রধান সুনির্দিষ্ট অবস্থান বা ক্লাস্টার কোনগুলো এবং প্রতিটিতে কোন ধরনের নক্ষত্র পাওয়া যায়?</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>(১) প্রধান ধারা (Main Sequence): কর্ণ বরাবর বাম-উপর থেকে ডান-নিচ পর্যন্ত বিস্তৃত অঞ্চল যেখানে প্রায় ৯০% নক্ষত্র (সূর্যসহ) তাদের কেন্দ্রের হাইড্রোজেন ফিউশন দ্বারা টিকে থাকে। (২) লোহিত দানব ও অতিদানব (Red Giants &amp; Supergiants): ডান-উপরের অঞ্চল; এরা শীতল ($T \sim 3000-4000\text{ K}$) হওয়া সত্ত্বেও এদের ব্যাসার্ধ বিশাল ($R \sim 100-1000 R_\odot$) হওয়ায় অত্যন্ত উজ্জ্বল দেখায় (উদা. বেটেলজিউস, আলদেবারান)। (৩) শ্বেত বামন (White Dwarfs): বাম-নিচের অঞ্চল; এরা অত্যন্ত উত্তপ্ত ($T &gt; 10,000\text{ K}$) কিন্তু আকার পৃথিবীর সমান অতিক্ষুদ্র হওয়ায় এদের ঔজ্জ্বল্য অতি ক্ষীণ।</t>
@@ -2813,11 +2663,6 @@
           <t>১৯২০ সালে ভারতীয় জ্যোতির্বিজ্ঞানী মেঘনাদ সাহা কর্তৃক উদ্ভাবিত বিখ্যাত 'সাহা আয়নন সমীকরণ'-এর মূল গুরুত্ব কী এবং এটি কীভাবে নক্ষত্রের বর্ণালী ব্যাখ্যা করে?</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>সাহা তাপীয় আয়নন সমীকরণ প্রমাণ করে যে নক্ষত্রের বর্ণালীতে নির্দিষ্ট শোষক রেখার তীব্রতা নক্ষত্রের রাসায়নিক উপাদানের পরিমাণের চেয়ে প্রধানত নক্ষত্রের বায়ুমণ্ডলের তাপমাত্রা এবং চাপের ওপর নির্ভরশীল: $\frac{N_{i+1} n_e}{N_i} = \frac{2 g_{i+1}}{g_i}\left(\frac{2\pi m_e k_B T}{h^2}\right)^{3/2} e^{-\chi_i / k_B T}$। সাহা সমীকরণ ব্যবহার করে সিসিলিয়া পেইন ১৯২৫ সালে প্রমাণ করেন যে সমস্ত নক্ষত্র এবং বিশ্বব্রহ্মাণ্ডের প্রধান উপাদান হলো হাইড্রোজেন এবং হিলিয়াম, যা আধুনিক জ্যোতিঃপদার্থবিজ্ঞানের সূচনা ঘটায়।</t>
@@ -2863,11 +2708,6 @@
           <t>সূর্যালোকে ফ্রনহফার রেখা (Fraunhofer Lines) কীভাবে উৎপন্ন হয় এবং এটি কীভাবে সূর্যের বায়ুমণ্ডলের রাসায়নিক গঠন প্রকাশ করে?</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>সূর্যের কেন্দ্র ও ফটোস্ফিয়ারের অত্যন্ত উত্তপ্ত ঘন প্লাজমা থেকে একটি অবিচ্ছিন্ন কৃষ্ণবস্তু বর্ণালী নির্গত হয়। এই আলো যখন সূর্যের বাইরের অপেক্ষাকৃত শীতল গ্যাসীয় বায়ুমণ্ডল (ক্রোমোস্ফিয়ার) ভেদ করে আসে, তখন বায়ুমণ্ডলে উপস্থিত বিভিন্ন মৌলের পরমাণুগুলো কেবল তাদের কোয়ান্টাম রূপান্তরের সাথে সম্পর্কিত সুনির্দিষ্ট তরঙ্গদৈর্ঘ্যের আলো শোষণ করে নেয়। ফলে অবিচ্ছিন্ন বর্ণালীর ওপর অন্ধকার শোষণ রেখা (Dark absorption lines) ফুটে ওঠে। প্রতিটি মৌলের শোষণ রেখা তার স্বতন্ত্র আঙুলের ছাপের (Fingerprint) মতো হওয়ায় ফ্রনহফার রেখা বিশ্লেষণ করে সূর্যের হাইড্রোজেন, হিলিয়াম, সোডিয়াম, আয়রন ইত্যাদির উপস্থিতি নিশ্চিত হওয়া যায়।</t>
@@ -2913,11 +2753,6 @@
           <t>একটি শীতল নক্ষত্রের পৃষ্ঠ তাপমাত্রা সূর্যের অর্ধেক ($T = 0.5 T_\odot$) কিন্তু এর ঔজ্জ্বল্য সূর্যের ১০০ গুণ ($L = 100 L_\odot$)। নক্ষত্রটির ব্যাসার্ধ সূর্যের ব্যাসার্ধের কত গুণ?</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>ঔজ্জ্বল্যের সূত্র: $\frac{L}{L_\odot} = \left(\frac{R}{R_\odot}\right)^2 \left(\frac{T}{T_\odot}\right)^4 \Rightarrow 100 = \left(\frac{R}{R_\odot}\right)^2 (0.5)^4 = \left(\frac{R}{R_\odot}\right)^2 \times 0.0625$। অতএব $\left(\frac{R}{R_\odot}\right)^2 = \frac{100}{0.0625} = 1600$। বর্গমূল করলে: $\frac{R}{R_\odot} = \sqrt{1600} = 40$। অর্থাৎ নক্ষত্রটির ব্যাসার্ধ সূর্যের ব্যাসার্ধের ৪০ গুণ (এটি একটি লোহিত দানব নক্ষত্র)।</t>
@@ -2961,11 +2796,6 @@
       <c r="G38" t="inlineStr">
         <is>
           <t>১৮৬৮ সালে ভারতে সূর্যগ্রহণ পর্যবেক্ষণের সময় ফরাসি জ্যোতির্বিজ্ঞানী জ্যানসেন এবং নরমান লকইয়ার কীভাবে পৃথিবীতে আবিষ্কারের পূর্বেই সূর্যে 'হিলিয়াম' মৌলটি আবিষ্কার করেছিলেন?</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3061,11 +2891,6 @@
           <t>একটি দূরবর্তী নক্ষত্রের বর্ণালীতে $\lambda_0 = 500.0\text{ nm}$ রেখাটি সামান্য সরে গিয়ে $\lambda = 500.1\text{ nm}$-এ দেখা গেল। নক্ষত্রটির দৃষ্টিরেখা বরাবর বেগ (Radial velocity) কত এবং এটি কি পৃথিবীর দিকে আসছে নাকি দূরে সরে যাচ্ছে?</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>ডপলার সরণ $\Delta\lambda = \lambda - \lambda_0 = 500.1 - 500.0 = +0.1\text{ nm}$। ডপলার সূত্র: $\frac{\Delta\lambda}{\lambda_0} = \frac{v_r}{c} \Rightarrow v_r = c \frac{\Delta\lambda}{\lambda_0}$। মান বসিয়ে: $v_r = (3 \times 10^5\text{ km/s}) \times \frac{0.1\text{ nm}}{500.0\text{ nm}} = 3 \times 10^5 \times 2 \times 10^{-4} = +60\text{ km/s}$। যেহেতু $\Delta\lambda &gt; 0$ (তরঙ্গদৈর্ঘ্য বৃদ্ধি বা রেডশিফট), সুতরাং নক্ষত্রটি পৃথিবী থেকে প্রতি সেকেন্ডে ৬০ কিমি বেগে দূরে সরে যাচ্ছে (Receding)।</t>
@@ -3111,11 +2936,6 @@
           <t>নক্ষত্রের ডপলার বর্ণালীমিতি বা দৃষ্টিরেখীয় বেগ পরিমাপ পদ্ধতি ব্যবহার করে কীভাবে কোনো অদৃশ্য বহির্গ্রহ (Exoplanet) আবিষ্কার করা সম্ভব হয়?</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>একটি নক্ষত্রকে কেন্দ্র করে কোনো গ্রহ ঘুরলে গ্রহের মহাকর্ষীয় আকর্ষণে নক্ষত্রটিও তাদের সাধারণ যৌথ ভরকেন্দ্রের (Barycenter) চারদিকে অতি ক্ষুদ্র বৃত্তাকারে দোলে (Wobble করে)। ফলে নক্ষত্রটি পর্যায়ক্রমে কখনো পৃথিবীর দিকে এগিয়ে আসে এবং কখনো দূরে সরে যায়। দূরবীক্ষণে নক্ষত্রের বর্ণালী রেখা পর্যবেক্ষণ করলে ডপলার ক্রিয়ার কারণে রেখাগুলো পর্যায়ক্রমিক ব্লু-শিফট ও রেড-শিফটে দুলতে থাকে। এই ক্ষুদ্র বেগের পরিবর্তন (কখনো মাত্র ১ মিটার/সেকেন্ড) মেপে অদৃশ্য গ্রহটির উপস্থিতি, ভর এবং কক্ষীয় পর্যায়কাল নির্ভুলভাবে বের করা যায় (যেমন ১৯৯৫ সালে 51 Pegasi b আবিষ্কার)।</t>
@@ -3161,11 +2981,6 @@
           <t>মহাজাগতিক গ্যাস ও ধূলিমেঘ সংকুচিত হয়ে নক্ষত্র গঠনের জন্য জেমস জিন্স কর্তৃক প্রতিপাদিত 'জিন্স ভর' (Jeans Mass - $M_J$) বলতে কী বোঝায় এবং শর্তটি কী?</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>একটি বিশাল আণবিক মেঘে (Giant Molecular Cloud) গ্যাসের অভ্যন্তরীণ তাপীয় চাপ মেঘটিকে প্রসারিত করতে চায় এবং মেঘটির নিজস্ব মহাকর্ষ বল একে সংকুচিত করতে চায়। মহাকর্ষীয় বল যখন অভ্যন্তরীণ গ্যাসীয় তাপীয় চাপকে অতিক্রম করে স্বতঃস্ফূর্ত পতন ঘটায়, সেই ন্যূনতম ভরকে জিন্স ভর বলে: $M &gt; M_J \approx \left(\frac{5 k_B T}{G \mu m_H}\right)^{3/2} \left(\frac{3}{4\pi\rho}\right)^{1/2}$। তাপমাত্রা $T$ যত কম এবং ঘনত্ব $\rho$ যত বেশি হয়, জিন্স ভর তত ছোট হয় এবং মেঘটি অতি সহজে খণ্ড খণ্ড হয়ে নক্ষত্র সৃষ্টির ধাপে প্রবেশ করে।</t>
@@ -3211,11 +3026,6 @@
           <t>আণবিক মেঘ পতনের পর 'প্রোটোস্টার' (Protostar) বা আদি-নক্ষত্র দশায় শক্তি উৎপাদনের প্রধান উৎস কী এবং এটি কীভাবে প্রধান ধারায় পৌঁছায়?</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>প্রোটোস্টার অবস্থায় কেন্দ্রের তাপমাত্রা ফিউশন ঘটানোর মতো উত্তপ্ত থাকে না। এই দশায় শক্তির একমাত্র উৎস হলো কেলভিন-হেলমহোল্টজ সংকোচন (Kelvin-Helmholtz contraction) অর্থাৎ মহাকর্ষীয় বিভব শক্তির তাপে রূপান্তর। মেঘটি ক্রমাগত সংকুচিত হতে থাকলে এর কেন্দ্র অত্যন্ত উত্তপ্ত ও ঘন হতে থাকে। সংকোচনজনিত তাপমাত্রা যখন কেন্দ্রে প্রায় ১ কোটি কেলভিনে ($10^7\text{ K}$) পৌঁছায়, তখন স্বতঃস্ফূর্ত হাইড্রোজেন ফিউশন প্রজ্বলিত হয়। ফিউশনজনিত বহির্মুখী বিকিরণ চাপ মহাকর্ষীয় সংকোচনকে রুখে দিয়ে স্থির সাম্যাবস্থা সৃষ্টি করে এবং নক্ষত্রটি প্রধান ধারায় (Main Sequence) প্রবেশ করে।</t>
@@ -3261,11 +3071,6 @@
           <t>নক্ষত্রের স্থিতিশীলতার মূল চাবিকাঠি 'হাইড্রোস্ট্যাটিক সাম্যাবস্থা'র ব্যবকলনীয় সমীকরণটি লেখো এবং এতে কোন দুটি বল পরস্পরকে ভারসাম্য করে?</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>সমীকরণ: $\frac{dP}{dr} = -\frac{G M(r)\rho(r)}{r^2}$। এখানে নক্ষত্রের কেন্দ্রের দিকে পরিচালিত প্রচণ্ড মহাকর্ষ বল (Inward gravitational pull) এবং কেন্দ্রের পারমাণবিক ফিউশন দ্বারা উৎপন্ন উত্তপ্ত গ্যাসের বহির্মুখী তাপীয় ও বিকিরণ চাপ নতি (Outward pressure gradient force) প্রতিটি স্তরে একে অপরকে নিখুঁতভাবে ভারসাম্য করে। যদি মহাকর্ষ বাড়ে, তবে নক্ষত্র সংকুচিত হয়ে উত্তপ্ত হয় ফলে চাপ বেড়ে যায়; আবার চাপ বাড়লে প্রসারিত হয়ে ঠান্ডা হয়। এই স্বনিয়ন্ত্রিত তাপীয় ভারসাম্যের কারণে নক্ষত্র বিলিয়ন বছর ধরে স্থিতিশীল আকারে থাকে।</t>
@@ -3311,11 +3116,6 @@
           <t>একটি গ্যাসীয় মেঘের ভর কত সৌর ভর ($M_\odot$)-এর কম হলে তা কখনই একটি পূর্ণাঙ্গ নক্ষত্রে পরিণত হতে পারে না? এই ব্যর্থ নক্ষত্রগুলোকে কী বলা হয়?</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>যদি কোনো প্রোটোস্টারের ভর সূর্যের ভরের প্রায় ৮% বা $0.08 M_\odot$ (বৃহস্পতির ভরের প্রায় ৮০ গুণ)-এর কম হয়, তবে তার কেন্দ্রে মহাকর্ষীয় সংকোচন পর্যাপ্ত তাপ তৈরি করার পূর্বেই ইলেকট্রন অবক্ষয় চাপ (Electron degeneracy pressure) সংকোচন থামিয়ে দেয়। কেন্দ্রের তাপমাত্রা কখনই স্থায়ী হাইড্রোজেন ফিউশনের জন্য প্রয়োজনীয় ১ কোটি কেলভিনে পৌঁছাতে পারে না। ফলে এরা কোনো দিন নক্ষত্র হিসেবে জ্বলে উঠতে পারে না; এই মহাজাগতিক ব্যর্থ বস্তুগুলোকে 'বাদামী বামন' (Brown Dwarfs) বলা হয়।</t>
@@ -3361,11 +3161,6 @@
           <t>একটি নক্ষত্রের সর্বোচ্চ সম্ভাব্য ঔজ্জ্বল্য বা ভরের প্রাকৃতিক সীমা 'এডিনটন সীমা' ($L_{\text{Edd}}$)-এর সমীকরণ কী এবং কোনো নক্ষত্র এই সীমা অতিক্রম করলে কী ঘটে?</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>নক্ষত্রের কেন্দ্র থেকে নির্গত আলোর ফোটনগুলো ইলেকট্রনের সাথে থমসন বিক্ষেপণের মাধ্যমে বহির্মুখী বিকিরণ চাপ (Radiation pressure) তৈরি করে। যখন এই বিকিরণ চাপ অন্তর্মুখী মহাকর্ষ বলের সমান হয়, সেই সর্বোচ্চ ঔজ্জ্বল্যকে এডিনটন ঔজ্জ্বল্য বলে: $L_{\text{Edd}} = \frac{4\pi G M c}{\kappa} = \frac{4\pi G M m_p c}{\sigma_T} \approx 3.2 \times 10^4 \left(\frac{M}{M_\odot}\right) L_\odot$। যদি কোনো অতি দানবীয় নক্ষত্রের ঔজ্জ্বল্য এই সীমা অতিক্রম করে ($L &gt; L_{\text{Edd}}$), তবে বিকিরণ চাপ মহাকর্ষকে উড়িয়ে দিয়ে নক্ষত্রের বাইরের স্তরগুলোকে তীব্র নাক্ষত্রিক বায়ু (Stellar wind) হিসেবে মহাশূন্যে উড়িয়ে দেয়, ফলে নক্ষত্রটি ভেঙে তার ভর কমাতে বাধ্য হয়।</t>
@@ -3411,11 +3206,6 @@
           <t>প্রধান ধারায় একটি নক্ষত্রের মোট জীবনকাল $t_{\text{ms}}$ তার ভরের ওপর কীভাবে নির্ভর করে? সূর্যের মোট জীবনকাল প্রায় ১০ বিলিয়ন বছর হলে সূর্যের ১০ গুণ ভরের নক্ষত্রের জীবনকাল কত হবে?</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>জীবনকাল হলো মোট উপলব্ধ পারমাণবিক জ্বালানি ($E \propto M$) এবং জ্বালানি ব্যয়ের হার বা ঔজ্জ্বল্যের ($L \propto M^{3.5}$) অনুপাত: $t_{\text{ms}} \propto \frac{M}{L} \propto \frac{M}{M^{3.5}} = M^{-2.5}$। সৌর এককে: $\frac{t}{t_\odot} \approx \left(\frac{M}{M_\odot}\right)^{-2.5}$। সূর্যের ক্ষেত্রে $t_\odot \approx 10^{10}\text{ বছর}$। ১০ গুণ ভরের নক্ষত্রের জন্য ($M = 10 M_\odot$): $t \approx 10^{10} \times 10^{-2.5} = \frac{10^{10}}{100 \sqrt{10}} \approx \frac{10^{10}}{316} \approx 3.16 \times 10^7\text{ বছর} \approx 32\text{ মিলিয়ন বছর}$। ভারী তারায় জ্বালানি বেশি থাকলেও তা প্রচণ্ড দ্রুত পোড়ায় বলে তার জীবনকাল নাটকীয়ভাবে কম হয়।</t>
@@ -3461,11 +3251,6 @@
           <t>সূর্যের মতো নক্ষত্রে কেন্দ্রের হাইড্রোজেন শেষ হয়ে গেলে এটি কীভাবে লোহিত দানবে (Red Giant) রূপান্তরিত হয় এবং 'হিলিয়াম ফ্ল্যাশ' (Helium Flash) কী?</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>কেন্দ্রে হাইড্রোজেন শেষ হলে ফিউশন বন্ধ হয়ে যায় এবং হিলিয়াম ছাই-এর কোর মহাকর্ষীয় টানে সংকুচিত হতে থাকে। কোরের সংকোচনে নির্গত তাপে কোরের ঠিক বাইরের হাইড্রোজেন শেলের ফিউশন তীব্র হয়, ফলে বহির্মুখী চাপে নক্ষত্রের বাইরের স্তরগুলো শতগুণ প্রসারিত হয়ে শীতল লাল বর্ণ ধারণ করে (লোহিত দানব)। সংকুচিত কোরে যখন তাপমাত্রা ১০ কোটি কেলভিনে ($10^8\text{ K}$) পৌঁছায়, তখন ট্রিপল-আলফা প্রক্রিয়ায় হিলিয়াম ফিউশন শুরু হয়। ইলেকট্রন অবক্ষয়িত কোরে কোনো তাপীয় সম্প্রসারণ না থাকায় কয়েক মিনিটের মধ্যে বিস্ফোরকভাবে বিপুল হিলিয়াম ফিউশন ঘটে; একে হিলিয়াম ফ্ল্যাশ বলে।</t>
@@ -3511,11 +3296,6 @@
           <t>লোহিত দানব নক্ষত্রের উত্তপ্ত হিলিয়াম কোরে তিনটি আলফা কণা ($^4\text{He}$) কীভাবে ফ্রেড হ্যয়েলের আবিষ্কৃত অনুনাদের মাধ্যমে কার্বন-১২ নিউক্লিয়াসে রূপান্তরিত হয়?</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>বিক্রিয়াটি দুটি ধাপে ঘটে: (১) দুটি আলফা কণা যুক্ত হয়ে অত্যন্ত ক্ষণস্থায়ী ($10^{-16}\text{ s}$) বেরিলিয়াম-৮ গঠন করে: $2 \, ^4\text{He} \rightleftharpoons \, ^8\text{Be}$। (২) বেরিলিয়াম-৮ ভেঙে যাওয়ার পূর্বেই তৃতীয় আরেকটি আলফা কণা একে আঘাত করে কার্বন-১২ তৈরি করে: $^8\text{Be} + \, ^4\text{He} \to \, ^{12}\text{C}^* \to \, ^{12}\text{C} + \gamma + 7.27\text{ MeV}$। ফ্রেড হ্যয়েল (Fred Hoyle) ১৯৫৩ সালে ভবিষ্যদ্বাণী করেছিলেন যে কার্বন-১২-এর ঠিক $7.65\text{ MeV}$-এ একটি কোয়ান্টাম অনুনাদী স্তর (Hoyle State) থাকতে হবে, যা ছাড়া মহাবিশ্বে কার্বন সৃষ্টি হওয়া অসম্ভব হতো।</t>
@@ -3561,11 +3341,6 @@
           <t>সূর্যের মতো মাঝারি নক্ষত্রের অন্তিম লোহিত দানব দশায় 'গ্রহীয় নীহারিকা' (Planetary Nebula) কীভাবে সৃষ্টি হয় এবং এর কেন্দ্রে কী অবশিষ্ট থাকে?</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>লোহিত দানব দশার শেষে কোরটিতে কার্বন ও অক্সিজেন জমা হয় কিন্তু সূর্যের ভর এত তাপমাত্রা তৈরি করতে পারে না যাতে কার্বন ফিউশন ঘটতে পারে। ফলে কোরের বাইরের স্তরে তীব্র তাপীয় স্পন্দন (Thermal pulses) সৃষ্টি হয়। এই স্পন্দনে নক্ষত্রের দুর্বল মহাকর্ষ কাটিয়ে এর সমগ্র বাইরের গ্যাসীয় খোলসটি মহাকাশে ধীরে ধীরে প্রতি সেকেন্ডে ২০-৩০ কিমি বেগে বিলীন হয়ে একটি প্রস্ফুটিত রঙিন গ্যাসীয় বুদ্বুদ গঠন করে; একে 'গ্রহীয় নীহারিকা' বলে (উদা. রিং নেবুলা)। এর ঠিক কেন্দ্রে নক্ষত্রের উত্তপ্ত উন্মুক্ত কার্বন-অক্সিজেন কোরটি একটি 'শ্বেত বামন' (White Dwarf) হিসেবে চিরতরে দৃশ্যমান থাকে।</t>
@@ -3646,7 +3421,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>হাবল সূত্র ও গ্যালাক্সির মন্দীভবন বেগ (সমস্যা 1)</t>
+          <t>জ্যোতির্বৈজ্ঞানিক দূরত্ব, হাবলের সূত্র ও মহাবিশ্ব (Distances, Hubble Law &amp; Cosmology)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3655,35 +3430,29 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>##PRESET:expanding-universe[size:medium]##
-[সমস্যা 1: হাবল সূত্র ও গ্যালাক্সির মন্দীভবন বেগ]
-##PRESET:expanding-universe[size:medium]##
-হাবল ধ্রুবকের মান $H_0 = 70\text{ km/s/Mpc}$ হলে আমাদের থেকে $d = 400\text{ Mpc}$ দূরে অবস্থিত একটি সর্পিলাকার গ্যালাক্সির অপসরণ বেগ (Recession velocity, $v = H_0 d$) কত?</t>
+          <t>##GEO:triangle[b=4,h=3][size:small]##
+একটি দূরবর্তী তারার লম্বন কোণ (Stellar Parallax) $p = 0.76\text{ arcsecond}$ (প্রক্সিমা সেন্টরাই)। পৃথিবী হতে তারাটির দূরত্ব: (ক) পারসেক ($	ext{pc}$), (খ) আলোকবর্ষ ($	ext{ly}$), এবং (গ) মিটারে নির্ণয় কর। ($1\text{ pc} = 3.26\text{ ly} = 3.086 \times 10^{16}\text{ m}$)।</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>##PRESET:expanding-universe[size:medium]##</t>
+          <t>##GEO:triangle[b=4,h=3][size:small]##</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 1)।</t>
+          <t>প্যারালাক্স দূরত্ব সমীকরণ: $d(\text{pc}) = \frac{1}{p(\text{arcsec})} = \frac{1}{0.76} \approx 1.3158\text{ pc}$। আলোকবর্ষে: $d = 1.3158 \times 3.26\text{ ly} \approx 4.2895\text{ ly} \approx 4.29\text{ ly}$। মিটারে: $d = 1.3158 \times (3.086 \times 10^{16}\text{ m}) \approx 4.0605 \times 10^{16}\text{ m}$।</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>(ক) দূরত্ব $d = 1.316\text{ pc}$, (খ) $d = 4.29\text{ ly}$, (গ) $d = 4.06 \times 10^{16}\text{ m}$</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3703,12 +3472,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>কৃষ্ণগহ্বরের সোয়ার্জশিল্ড ব্যাসার্ধ (সমস্যা 2)</t>
+          <t>জ্যোতির্বৈজ্ঞানিক দূরত্ব, হাবলের সূত্র ও মহাবিশ্ব (Distances, Hubble Law &amp; Cosmology)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -3716,31 +3485,25 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>##PRESET:black-hole-event-horizon[size:medium]##
-[সমস্যা 2: কৃষ্ণগহ্বরের সোয়ার্জশিল্ড ব্যাসার্ধ]
-##PRESET:black-hole-event-horizon[size:medium]##
-সূর্যের ভরের 6 গুণ ভরবিশিষ্ট একটি মৃত নক্ষত্র সংকুচিত হয়ে ব্ল্যাকহোলে পরিণত হলে এর ঘটনা দিগন্তের সোয়ার্জশিল্ড ব্যাসার্ধ ($R_s = \frac{2GM}{c^2}$) কত কিলোমিটার হবে? ($M_\odot = 2.0 \times 10^{30}\text{ kg}$)</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি গ্যালাক্সি হতে আগত আলোর হাইড্রোজেন $	ext{H}_lpha$ বর্ণালী রেখার প্রকৃত তরঙ্গদৈর্ঘ্য $\lambda_0 = 656.3\text{ nm}$ পৃথিবীতে পরিমাপ করে পাওয়া গেল $\lambda = 672.7\text{ nm}$। (ক) গ্যালাক্সিটির রেডশিফট (Redshift $z$), (খ) গ্যালাক্সিটির অপসরণ বেগ $v$, এবং (গ) হাবলের ধ্রুবক $H_0 = 70\text{ km/s/Mpc}$ ধরে পৃথিবী হতে গ্যালাক্সিটির দূরত্ব নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>##PRESET:black-hole-event-horizon[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 2)।</t>
+          <t>রেডশিফট $z = \frac{\Delta\lambda}{\lambda_0} = \frac{672.7 - 656.3}{656.3} = \frac{16.4}{656.3} \approx 0.024988 \approx 0.0250$। ডপলার বেগ $v = z c = 0.0250 \times (3.0 \times 10^5\text{ km/s}) = 7500.0\text{ km/s}$। হাবলের সূত্র: $v = H_0 d \implies d = \frac{v}{H_0} = \frac{7500\text{ km/s}}{70\text{ km/s/Mpc}} \approx 107.14\text{ Mpc}$। আলোকবর্ষে: $107.14 \times 3.26 \times 10^6 \approx 3.49 \times 10^8\text{ ly}$।</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 2</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>(ক) $z = 0.0250$, (খ) অপসরণ বেগ $v = 7500.0\text{ km/s}$, (গ) দূরত্ব $d = 107.14\text{ Mpc} = 3.49 \times 10^8\text{ ly}$</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3760,7 +3523,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>নাক্ষত্রিক প্যারালাক্স ও পারসেক দূরত্ব (সমস্যা 3)</t>
+          <t>জ্যোতির্বৈজ্ঞানিক দূরত্ব, হাবলের সূত্র ও মহাবিশ্ব (Distances, Hubble Law &amp; Cosmology)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3769,29 +3532,29 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>[সমস্যা 3: নাক্ষত্রিক প্যারালাক্স ও পারসেক দূরত্ব]
-একটি দূরবর্তী নক্ষত্রের বার্ষিক প্যারালাক্স কোণ $p = 0.08''$ (আর্কসেকেন্ড)। নক্ষত্রটির দূরত্ব পারসেক (pc) এবং আলোকবর্ষে (ly) কত হবে? ($d = 1/p$)</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+হাবল ধ্রুবকের মান $H_0 = 70.0\text{ km}\cdot\text{s}^{-1}\cdot\text{Mpc}^{-1}$ ধরে মহাবিশ্বের আনুমানিক বয়স (Hubble Time $t_H = 1/H_0$) বিলিয়ন বছরে নির্ণয় কর। ($1\text{ Mpc} = 3.086 \times 10^{19}\text{ km}$)।</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 3)।</t>
+          <t>$H_0$-কে এসআই এককে রূপান্তর: $H_0 = \frac{70.0\text{ km/s}}{3.086 \times 10^{19}\text{ km}} \approx 2.2683 \times 10^{-18}\text{ s}^{-1}$। মহাবিশ্বের বয়স $t_H = \frac{1}{H_0} = \frac{1}{2.2683 \times 10^{-18}\text{ s}^{-1}} \approx 4.4086 \times 10^{17}\text{ s}$। বছরে রূপান্তর: $t_H = \frac{4.4086 \times 10^{17}}{3.1536 \times 10^7\text{ s/yr}} \approx 1.398 \times 10^{10}\text{ বছর} = 13.98\text{ বিলিয়ন বছর}$।</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 3</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>মহাবিশ্বের বয়স $t_H \approx 13.98\text{ বিলিয়ন বছর} \approx 14.0\text{ Gyr}$</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3811,12 +3574,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>নক্ষত্রের উজ্জ্বলতা ও বিপরীত বর্গীয় সূত্র (সমস্যা 4)</t>
+          <t>জ্যোতির্বৈজ্ঞানিক দূরত্ব, হাবলের সূত্র ও মহাবিশ্ব (Distances, Hubble Law &amp; Cosmology)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -3824,25 +3587,25 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>[সমস্যা 4: নক্ষত্রের উজ্জ্বলতা ও বিপরীত বর্গীয় সূত্র]
-একটি নক্ষত্রের ঔজ্জ্বল্য পৃথিবীর সাপেক্ষে পরিমাপ করা হলো। যদি নক্ষত্রটির দূরত্ব 10 গুণ বৃদ্ধি পায়, তবে পৃথিবীতে এর আপাত উজ্জ্বলতা কত গুণ হ্রাস পাবে?</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি তারার দৃশ্যমান মান (Apparent magnitude) $m = +6.0$ এবং পরম মান (Absolute magnitude) $M = +1.0$। দূরত্ব মডিউলাস সমীকরণ $m - M = 5\log_{10}(d) - 5$ ব্যবহার করে পৃথিবী হতে তারাটির দূরত্ব পারসেকে নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 4)।</t>
+          <t>দূরত্ব মডিউলাস: $m - M = 6.0 - 1.0 = 5.0$। $5.0 = 5\log_{10}(d) - 5 \implies 5\log_{10}(d) = 10.0 \implies \log_{10}(d) = 2.0 \implies d = 10^2 = 100.0\text{ pc}$। আলোকবর্ষে: $d = 100 \times 3.26 = 326.0\text{ ly}$।</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 4</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>দূরত্ব $d = 100.0\text{ pc} = 326.0\text{ ly}$</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3862,7 +3625,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ভীনের সরণ সূত্র ও নক্ষত্রের পৃষ্ঠ তাপমাত্রা (সমস্যা 5)</t>
+          <t>জ্যোতির্বৈজ্ঞানিক দূরত্ব, হাবলের সূত্র ও মহাবিশ্ব (Distances, Hubble Law &amp; Cosmology)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3871,29 +3634,29 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>[সমস্যা 5: ভীনের সরণ সূত্র ও নক্ষত্রের পৃষ্ঠ তাপমাত্রা]
-সূর্যের বিকিরণ বর্ণালীতে সর্বোচ্চ তীব্রতার তরঙ্গদৈর্ঘ্য $\lambda_{max} = 5000\text{ \AA}$। অন্য একটি নক্ষত্রের সর্বোচ্চ তীব্রতার তরঙ্গদৈর্ঘ্য $12000\text{ \AA}$ হলে নক্ষত্রটির পৃষ্ঠের তাপমাত্রা কত? (সূর্যের তাপমাত্রা $6000\text{ K}$)</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+পগসনের সূত্রানুযায়ী দুটি তারার আপাত উজ্জ্বলতার অনুপাত $F_1 / F_2 = 100$ হলে তাদের দৃশ্যমান আপাত মানের পার্থক্য $m_2 - m_1$ কত?</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 5)।</t>
+          <t>পগসনের সূত্র: $m_2 - m_1 = 2.5 \log_{10}\left(\frac{F_1}{F_2}\right) = 2.5 \log_{10}(100) = 2.5(2) = 5.0$। অর্থাৎ ৫ মানের পার্থক্যে উজ্জ্বলতার অনুপাত ঠিক ১০০ গুণ হয়।</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 5</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>মানের পার্থক্য $m_2 - m_1 = 5.0$ মান</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3913,12 +3676,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>স্টিফান-বোল্টজম্যান সূত্র ও নক্ষত্রের দীপ্তি (সমস্যা 6)</t>
+          <t>জ্যোতির্বৈজ্ঞানিক দূরত্ব, হাবলের সূত্র ও মহাবিশ্ব (Distances, Hubble Law &amp; Cosmology)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -3926,25 +3689,25 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>[সমস্যা 6: স্টিফান-বোল্টজম্যান সূত্র ও নক্ষত্রের দীপ্তি]
-একটি নক্ষত্রের ব্যাসার্ধ সূর্যের ব্যাসার্ধের দ্বিগুণ এবং পৃষ্ঠের তাপমাত্রা সূর্যের তাপমাত্রার 2 গুণ। নক্ষত্রটির সামগ্রিক দীপ্তি (Luminosity) সূর্যের তুলনায় কত গুণ হবে? ($L \propto R^2 T^4$)</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি তারার পৃষ্ঠের তাপমাত্রা সূর্যের পৃষ্ঠের তাপমাত্রার দ্বিগুণ ($T_* = 2 T_\odot$) এবং এর ব্যাসার্ধ সূর্যের ব্যাসার্ধের তিনগুণ ($R_* = 3 R_\odot$)। স্টিফেন-বোল্টজম্যান সূত্রানুযায়ী তারাটির দীপ্তি (Luminosity $L_*$) সূর্যের দীপ্তির কত গুণ?</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 6)।</t>
+          <t>তারার দীপ্তি $L = 4\pi R^2 \sigma T^4 \propto R^2 T^4$। অনুপাত: $\frac{L_*}{L_\odot} = \left(\frac{R_*}{R_\odot}\right)^2 \left(\frac{T_*}{T_\odot}\right)^4 = 3^2 \times 2^4 = 9 \times 16 = 144.0$।</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 6</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>দীপ্তি $L_* = 144.0 L_\odot$ (সূর্যের ১৪৪ গুণ)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3964,7 +3727,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>চন্দ্রশেখর সীমা ও শ্বেত বামন নক্ষত্র (সমস্যা 7)</t>
+          <t>জ্যোতির্বৈজ্ঞানিক দূরত্ব, হাবলের সূত্র ও মহাবিশ্ব (Distances, Hubble Law &amp; Cosmology)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3973,29 +3736,29 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>[সমস্যা 7: চন্দ্রশেখর সীমা ও শ্বেত বামন নক্ষত্র]
-সূর্যের ভরের ১.৪ গুণ ভর ($1.4 M_\odot$) চন্দ্রশেখর সীমা নামে পরিচিত। $M = 4.0 M_\odot$ ভরের একটি নক্ষত্রের মৃত্যুর পর এর সম্ভাব্য রূপ কী হবে—শ্বেত বামন, নিউট্রন স্টার না ব্ল্যাকহোল?</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+ভীনের সরণ সূত্রানুযায়ী একটি তারার বর্ণালীর সর্বোচ্চ বিকিরণ তীব্রতার তরঙ্গদৈর্ঘ্য $\lambda_{\max} = 483\text{ nm}$। তারাটির পৃষ্ঠের কার্যকর তাপমাত্রা কত কেলভিন? ($b = 2.898 \times 10^{-3}\text{ m}\cdot\text{K}$)।</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 7)।</t>
+          <t>ভীনের সূত্র: $\lambda_{\max} T = b \implies T = \frac{b}{\lambda_{\max}} = \frac{2.898 \times 10^{-3}\text{ m}\cdot\text{K}}{483 \times 10^{-9}\text{ m}} = \frac{2898 \times 10^{-6}}{0.483 \times 10^{-6}} = 6000.0\text{ K}$ (এটি সূর্যের পৃষ্ঠ তাপমাত্রার প্রায় সমান)।</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 7</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>পৃষ্ঠ তাপমাত্রা $T = 6000.0\text{ K}$</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4015,12 +3778,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>মহাবিশ্বের আনুমানিক বয়স নির্ণয় (সমস্যা 8)</t>
+          <t>জ্যোতির্বৈজ্ঞানিক দূরত্ব, হাবলের সূত্র ও মহাবিশ্ব (Distances, Hubble Law &amp; Cosmology)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -4028,25 +3791,25 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>[সমস্যা 8: মহাবিশ্বের আনুমানিক বয়স নির্ণয়]
-হাবল ধ্রুবক $H_0 = 60\text{ km/s/Mpc}$ হলে হাবল সময়ের সূত্রানুসারে ($t = 1/H_0$) আমাদের মহাবিশ্বের আনুমানিক বয়স কত বিলিয়ন বছর হবে?</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+সূর্যের ভর $M_\odot = 2.0 	imes 10^{30}\text{ kg}$। সূর্য যদি সংকুচিত হয়ে একটি কৃষ্ণগহ্বরে (Black Hole) পরিণত হয়, তবে এর সোয়ার্জশিল্ড ব্যাসার্ধ (Schwarzschild radius $R_s$) কত কিলোমিটার হবে? ($G = 6.674 \times 10^{-11}\text{ N}\cdot\text{m}^2/\text{kg}^2$)।</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 8)।</t>
+          <t>ঘটনা দিগন্তের ব্যাসার্ধ $R_s = \frac{2 G M}{c^2} = \frac{2 \times (6.674 \times 10^{-11}) \times (2.0 \times 10^{30})}{(3.0 \times 10^8)^2} = \frac{2.6696 \times 10^{20}}{9.0 \times 10^{16}} \approx 2966.2\text{ m} \approx 2.97\text{ km}$।</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 8</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>সোয়ার্জশিল্ড ব্যাসার্ধ $R_s = 2.966\text{ km} \approx 3.0\text{ km}$</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4066,7 +3829,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>নক্ষত্রের লাল সরণ ও ডপলার প্রভাব (সমস্যা 9)</t>
+          <t>জ্যোতির্বৈজ্ঞানিক দূরত্ব, হাবলের সূত্র ও মহাবিশ্ব (Distances, Hubble Law &amp; Cosmology)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4075,29 +3838,29 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>[সমস্যা 9: নক্ষত্রের লাল সরণ ও ডপলার প্রভাব]
-একটি দূরবর্তী কোয়াসার হতে আগত হাইড্রোজেন $\text{H}_\alpha$ বর্ণালী রেখার প্রকৃত তরঙ্গদৈর্ঘ্য $6563\text{ \AA}$ কিন্তু পৃথিবীতে পরিমাপকৃত মান $8000\text{ \AA}$। কোয়াসারটির লাল সরণ ($z = \Delta\lambda / \lambda$) কত?</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+চন্দ্রশেখর সীমা (Chandrasekhar Limit) কী এবং এর মান কত? এই সীমার চেয়ে অধিক ভরের মৃত নক্ষত্রের চূড়ান্ত পরিণতি কী হয়?</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 9)।</t>
+          <t>১৯৩০ সালে সুব্রহ্মণ্যম চন্দ্রশেখর আপেক্ষিক কোয়ান্টাম বলবিদ্যার ভিত্তিতে প্রমাণ করেন যে ইলেকট্রন অপজাত্য চাপ (Electron degeneracy pressure) সর্বোচ্চ $1.44 M_\odot$ (সৌর ভর) পর্যন্ত নিউক্লিয়াসকে মহাকর্ষীয় পতনের হাত থেকে ধরে রাখতে পারে। এই সীমার অধিক ভরের নক্ষত্র সুপারনোভা বিস্ফোরণের পর আরও সংকুচিত হয়ে নিউট্রন তারা (পালসার) অথবা চরম ক্ষেত্রে কৃষ্ণগহ্বরে পরিণত হয়।</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 9</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>চন্দ্রশেখর সীমা $M \approx 1.44 M_\odot$; এই সীমার বেশি ভরের নক্ষত্র শ্বেত বামন হতে পারে না, তা নিউট্রন তারা বা কৃষ্ণগহ্বরে পরিণত হয়</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4117,12 +3880,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>মহাজাগতিক পটভূমি বিকিরণ (CMBR) (সমস্যা 10)</t>
+          <t>জ্যোতির্বৈজ্ঞানিক দূরত্ব, হাবলের সূত্র ও মহাবিশ্ব (Distances, Hubble Law &amp; Cosmology)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -4130,25 +3893,25 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>[সমস্যা 10: মহাজাগতিক পটভূমি বিকিরণ (CMBR)]
-মহাজাগতিক পটভূমি বিকিরণের বর্তমান তাপমাত্রা $T = 2.710\text{ K}$। ভীনের সূত্র $\lambda_{max} T = 2.898 \times 10^{-3}\text{ m}\cdot\text{K}$ দ্বারা এই বিকিরণের শীর্ষ তরঙ্গদৈর্ঘ্য কোন অঞ্চলে পড়ে হিসাব কর।</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+মহাজাগতিক অণুতরঙ্গ পটভূমি বিকিরণ (Cosmic Microwave Background Radiation, CMBR) বলতে কী বোঝায় এবং এটি কীভাবে মহাবিস্ফোরণ (Big Bang) তত্ত্বের সবচেয়ে শক্তিশালী প্রমাণ প্রদান করে?</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 10)।</t>
+          <t>১৯৬৫ সালে পেনজিয়াস ও উইলসন কর্তৃক আবিষ্কৃত এই বিকিরণ প্রমাণ করে যে আদিম মহাবিশ্ব অত্যন্ত উত্তপ্ত ও ঘন ছিল। পুনর্মিলন যুগে (Recombination era) ইলেকট্রন ও প্রোটন যুক্ত হয়ে হাইড্রোজেন গঠনের পর আলো মহাবিশ্বে মুক্তভাবে চলাচল শুরু করে। স্থানকালের প্রসারণে এই ফোটনগুলোর তরঙ্গদৈর্ঘ্য ১০০০ গুণের বেশি প্রসারিত হয়ে বর্তমানে মাইক্রোওয়েভ অঞ্চলের নিখুঁত $2.725\text{ K}$ কৃষ্ণবস্তু বিকিরণে পরিণত হয়েছে।</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 10</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>মহাবিস্ফোরণের প্রায় ৩,৮০,০০০ বছর পরের আদিম ফোটন বিকিরণ যা মহাবিশ্বের প্রসারণে প্রসারিত হয়ে বর্তমানে $T \approx 2.73\text{ K}$ ব্ল্যাকবডি বিকিরণ হিসেবে মহাশূন্যে সমসত্ত্বভাবে বিদ্যমান</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4168,44 +3931,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>হাবল সূত্র ও গ্যালাক্সির মন্দীভবন বেগ (সমস্যা 11)</t>
+          <t>নক্ষত্রের বিবর্তন, কৃষ্ণগহ্বর ও মহাজাগতিক গতিবিদ্যা (Stellar Evolution &amp; Black Holes)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>##PRESET:expanding-universe[size:medium]##
-[সমস্যা 11: হাবল সূত্র ও গ্যালাক্সির মন্দীভবন বেগ]
-##PRESET:expanding-universe[size:medium]##
-হাবল ধ্রুবকের মান $H_0 = 70\text{ km/s/Mpc}$ হলে আমাদের থেকে $d = 1200\text{ Mpc}$ দূরে অবস্থিত একটি সর্পিলাকার গ্যালাক্সির অপসরণ বেগ (Recession velocity, $v = H_0 d$) কত?</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি সুপারম্যাসিভ ব্ল্যাক হোলের ভর $M = 4.0 	imes 10^6 M_\odot$ (আমাদের মিল্কিওয়ে গ্যালাক্সির কেন্দ্রস্থ ধনু $A^*$ / Sagittarius $A^*$)। এর সোয়ার্জশিল্ড ঘটনা দিগন্তের ব্যাসার্ধ কত কিলোমিটার ও কত জ্যোতির্বৈজ্ঞানিক একক ($	ext{AU}$)? ($1	ext{ AU} pprox 1.50 	imes 10^8	ext{ km}$)।</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>##PRESET:expanding-universe[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 11)।</t>
+          <t>$R_s = \frac{2 G M}{c^2} = (4.0 \times 10^6) \times R_s(\text{Sun}) = (4.0 \times 10^6) \times (2.966\text{ km}) \approx 1.186 \times 10^7\text{ km}$। $\text{AU}$-তে: $R_s = \frac{1.186 \times 10^7\text{ km}}{1.496 \times 10^8\text{ km/AU}} \approx 0.0793\text{ AU}$।</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 11</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>ব্যাসার্ধ $R_s = 1.186 \times 10^7\text{ km} \approx 0.079\text{ AU}$ (সূর্য ও বুধের দূরত্বের প্রায় এক-পঞ্চমাংশ)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4225,7 +3982,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>কৃষ্ণগহ্বরের সোয়ার্জশিল্ড ব্যাসার্ধ (সমস্যা 12)</t>
+          <t>নক্ষত্রের বিবর্তন, কৃষ্ণগহ্বর ও মহাজাগতিক গতিবিদ্যা (Stellar Evolution &amp; Black Holes)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4238,31 +3995,26 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>##PRESET:black-hole-event-horizon[size:medium]##
-[সমস্যা 12: কৃষ্ণগহ্বরের সোয়ার্জশিল্ড ব্যাসার্ধ]
-##PRESET:black-hole-event-horizon[size:medium]##
-সূর্যের ভরের 2 গুণ ভরবিশিষ্ট একটি মৃত নক্ষত্র সংকুচিত হয়ে ব্ল্যাকহোলে পরিণত হলে এর ঘটনা দিগন্তের সোয়ার্জশিল্ড ব্যাসার্ধ ($R_s = \frac{2GM}{c^2}$) কত কিলোমিটার হবে? ($M_\odot = 2.0 \times 10^{30}\text{ kg}$)</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি নিউট্রন তারার ভর $M = 2.0 M_\odot = 4.0 	imes 10^{30}\text{ kg}$ এবং ব্যাসার্ধ $R = 10.0\text{ km}$। নিউট্রন তারাটির পৃষ্ঠে অভিকর্ষজ ত্বরণ $g_*$ এবং গড় ঘনত্ব $+ho$ নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>##PRESET:black-hole-event-horizon[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 12)।</t>
+          <t>অভিকর্ষজ ত্বরণ $g_* = \frac{G M}{R^2} = \frac{(6.674 \times 10^{-11}) \times (4.0 \times 10^{30})}{(1.0 \times 10^4)^2} = \frac{2.6696 \times 10^{20}}{1.0 \times 10^8} \approx 2.67 \times 10^{12}\text{ m/s}^2$। আয়তন $V = \frac{4}{3}\pi R^3 = \frac{4}{3}\pi (10^4)^3 \approx 4.189 \times 10^{12}\text{ m}^3$। ঘনত্ব $\rho = \frac{M}{V} = \frac{4.0 \times 10^{30}}{4.189 \times 10^{12}} \approx 9.55 \times 10^{17}\text{ kg/m}^3$ (নিউক্লিয়াসের ঘনত্বের চেয়েও বেশি)।</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 12</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>পৃষ্ঠ ত্বরণ $g_* = 2.67 \times 10^{12}\text{ m/s}^2$ (পৃথিবীর চেয়ে ২৭০ বিলিয়ন গুণ), গড় ঘনত্ব $\rho = 9.55 \times 10^{17}\text{ kg/m}^3$</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4282,38 +4034,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>নাক্ষত্রিক প্যারালাক্স ও পারসেক দূরত্ব (সমস্যা 13)</t>
+          <t>নক্ষত্রের বিবর্তন, কৃষ্ণগহ্বর ও মহাজাগতিক গতিবিদ্যা (Stellar Evolution &amp; Black Holes)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>[সমস্যা 13: নাক্ষত্রিক প্যারালাক্স ও পারসেক দূরত্ব]
-একটি দূরবর্তী নক্ষত্রের বার্ষিক প্যারালাক্স কোণ $p = 0.04''$ (আর্কসেকেন্ড)। নক্ষত্রটির দূরত্ব পারসেক (pc) এবং আলোকবর্ষে (ly) কত হবে? ($d = 1/p$)</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি পালসার (ঘূর্ণায়মান নিউট্রন তারা) প্রতি সেকেন্ডে $50$ বার নিজ অক্ষের সাপেক্ষে ঘোরে ($f = 50\text{ Hz}$)। এর ব্যাসার্ধ $12.0\text{ km}$ হলে বিষুবীয় অঞ্চলের রৈখিক বেগ আলোর বেগের শতকরা কত ভাগ?</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 13)।</t>
+          <t>কৌণিক বেগ $\omega = 2\pi f = 2\pi(50) = 100\pi \approx 314.16\text{ rad/s}$। বিষুবীয় দ্রুতি $v = \omega R = (314.16\text{ rad/s}) \times 12000\text{ m} \approx 3.77 \times 10^6\text{ m/s} = 3770\text{ km/s}$। আলোর বেগের অনুপাত $\frac{v}{c} = \frac{3.77 \times 10^6}{3.0 \times 10^8} \approx 0.01257 = 1.26\%$।</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 13</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>রৈখিক দ্রুতি $v = 3770.0\text{ km/s} \approx 1.26\% c$</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4333,7 +4085,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>নক্ষত্রের উজ্জ্বলতা ও বিপরীত বর্গীয় সূত্র (সমস্যা 14)</t>
+          <t>নক্ষত্রের বিবর্তন, কৃষ্ণগহ্বর ও মহাজাগতিক গতিবিদ্যা (Stellar Evolution &amp; Black Holes)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4346,25 +4098,25 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>[সমস্যা 14: নক্ষত্রের উজ্জ্বলতা ও বিপরীত বর্গীয় সূত্র]
-একটি নক্ষত্রের ঔজ্জ্বল্য পৃথিবীর সাপেক্ষে পরিমাপ করা হলো। যদি নক্ষত্রটির দূরত্ব 6 গুণ বৃদ্ধি পায়, তবে পৃথিবীতে এর আপাত উজ্জ্বলতা কত গুণ হ্রাস পাবে?</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি শ্বেত বামন নক্ষত্রের ভর সূর্যের সমান ($M = 1.0 M_\odot$) কিন্তু এর আকার পৃথিবীর সমান ($R pprox 6400\text{ km}$)। এর পৃষ্ঠে একটি $1.0\text{ kg}$ ভরের বস্তুর ওজন কত নিউটন হবে?</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 14)।</t>
+          <t>পৃষ্ঠ ত্বরণ $g = \frac{G M}{R^2} = \frac{(6.674 \times 10^{-11}) \times (2.0 \times 10^{30})}{(6.4 \times 10^6)^2} = \frac{1.3348 \times 10^{20}}{4.096 \times 10^{13}} \approx 3.259 \times 10^6\text{ m/s}^2$। $1\text{ kg}$ ভরের ওজন $W = mg = 1.0 \times (3.259 \times 10^6) \approx 3.26 \times 10^6\text{ N}$।</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 14</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>ওজন $W \approx 3.26 \times 10^6\text{ N}$ (প্রায় ৩২৬ টন বলের সমান)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4384,38 +4136,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ভীনের সরণ সূত্র ও নক্ষত্রের পৃষ্ঠ তাপমাত্রা (সমস্যা 15)</t>
+          <t>নক্ষত্রের বিবর্তন, কৃষ্ণগহ্বর ও মহাজাগতিক গতিবিদ্যা (Stellar Evolution &amp; Black Holes)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>[সমস্যা 15: ভীনের সরণ সূত্র ও নক্ষত্রের পৃষ্ঠ তাপমাত্রা]
-সূর্যের বিকিরণ বর্ণালীতে সর্বোচ্চ তীব্রতার তরঙ্গদৈর্ঘ্য $\lambda_{max} = 5000\text{ \AA}$। অন্য একটি নক্ষত্রের সর্বোচ্চ তীব্রতার তরঙ্গদৈর্ঘ্য $8000\text{ \AA}$ হলে নক্ষত্রটির পৃষ্ঠের তাপমাত্রা কত? (সূর্যের তাপমাত্রা $6000\text{ K}$)</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি কোয়েসার (Quasar) $z = 0.50$ রেডশিফটে ধাবমান। আপেক্ষিক ডপলার সূত্র $1 + z = \sqrt{rac{1 + v/c}{1 - v/c}}$ ব্যবহার করে কোয়েসারটির অপসরণ দ্রুতি $v$ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 15)।</t>
+          <t>$1 + z = 1 + 0.50 = 1.50$। উভয়পক্ষে বর্গ করে: $\frac{1 + v/c}{1 - v/c} = (1.50)^2 = 2.25$। বজ্রগুণন করে: $1 + v/c = 2.25(1 - v/c) = 2.25 - 2.25 v/c \implies 3.25 v/c = 1.25 \implies \frac{v}{c} = \frac{1.25}{3.25} = \frac{5}{13} \approx 0.3846$। দ্রুতি $v \approx 0.3846 c \approx 1.154 \times 10^8\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 15</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>অপসরণ দ্রুতি $v = 0.3846 c = 1.154 \times 10^8\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4435,7 +4187,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>স্টিফান-বোল্টজম্যান সূত্র ও নক্ষত্রের দীপ্তি (সমস্যা 16)</t>
+          <t>নক্ষত্রের বিবর্তন, কৃষ্ণগহ্বর ও মহাজাগতিক গতিবিদ্যা (Stellar Evolution &amp; Black Holes)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4448,25 +4200,27 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>[সমস্যা 16: স্টিফান-বোল্টজম্যান সূত্র ও নক্ষত্রের দীপ্তি]
-একটি নক্ষত্রের ব্যাসার্ধ সূর্যের ব্যাসার্ধের দ্বিগুণ এবং পৃষ্ঠের তাপমাত্রা সূর্যের তাপমাত্রার 10 গুণ। নক্ষত্রটির সামগ্রিক দীপ্তি (Luminosity) সূর্যের তুলনায় কত গুণ হবে? ($L \propto R^2 T^4$)</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+মহাজাগতিক ক্রিটিক্যাল ঘনত্ব (Critical Density of the Universe): মহাবিশ্বের প্রসারণ থামিয়ে সমতল মহাবিশ্ব বজায় রাখার জন্য ক্রিটিক্যাল ঘনত্বের সমীকরণ $+ho_c = rac{3 H_0^2}{8\pi G}$ প্রতিপাদন কর। $H_0 = 70\text{ km/s/Mpc}$ হলে $+ho_c$-এর মান কত?</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 16)।</t>
+          <t>ব্যাসার্ধ $R$-এর মহাজাগতিক গোলকের মুক্তিবেগ $v = H_0 R$ হলে: $\frac{1}{2}m v^2 = \frac{G M m}{R} \implies \frac{1}{2}(H_0 R)^2 = \frac{G (\frac{4}{3}\pi R^3 \rho_c)}{R} \implies \frac{1}{2}H_0^2 = \frac{4}{3}\pi G \rho_c \implies \rho_c = \frac{3 H_0^2}{8\pi G}$। $H_0 = 2.268 \times 10^{-18}\text{ s}^{-1}$ বসালে: $\rho_c = \frac{3 (2.268 \times 10^{-18})^2}{8\pi (6.674 \times 10^{-11})} = \frac{1.543 \times 10^{-35}}{1.677 \times 10^{-9}} \approx 9.20 \times 10^{-27}\text{ kg/m}^3$।</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 16</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+          <t>ক্রিটিক্যাল ঘনত্ব $\rho_c = 9.20 \times 10^{-27}\text{ kg/m}^3$ (প্রতি ঘনমিটারে প্রায় ৫-৬টি হাইড্রোজেন পরমাণু)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4486,38 +4240,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>চন্দ্রশেখর সীমা ও শ্বেত বামন নক্ষত্র (সমস্যা 17)</t>
+          <t>নক্ষত্রের বিবর্তন, কৃষ্ণগহ্বর ও মহাজাগতিক গতিবিদ্যা (Stellar Evolution &amp; Black Holes)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>[সমস্যা 17: চন্দ্রশেখর সীমা ও শ্বেত বামন নক্ষত্র]
-সূর্যের ভরের ১.৪ গুণ ভর ($1.4 M_\odot$) চন্দ্রশেখর সীমা নামে পরিচিত। $M = 12.0 M_\odot$ ভরের একটি নক্ষত্রের মৃত্যুর পর এর সম্ভাব্য রূপ কী হবে—শ্বেত বামন, নিউট্রন স্টার না ব্ল্যাকহোল?</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+ডার্ক ম্যাটার (Dark Matter) এবং গ্যালাক্সির ঘূর্ণন বক্ররেখা (Galactic rotation curves): ভেরা রুবিনের পর্যবেক্ষণ অনুসারে গ্যালাক্সির কেন্দ্র হতে বাইরের দিকে তারাদের কক্ষীয় দ্রুতি কেপলারীয় সূত্র $v \propto 1/\sqrt{r}$ না মেনে প্রায় স্থির ধ্রুবক কেন থাকে?</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 17)।</t>
+          <t>যদি কেবল দৃশ্যমান নক্ষত্রমণ্ডলীতে ভর সীমাবদ্ধ থাকত তবে বাইরের তারার বেগ দূরত্বের সাথে হ্রাস পাওয়ার কথা ছিল ($v = \sqrt{GM/r} \propto 1/\sqrt{r}$)। কিন্তু বাস্তবে দেখা যায় বাইরের তারার বেগ ধ্রুব বা ফ্ল্যাট থাকে ($v \approx \text{const}$), যার অর্থ হলো দূরত্বের সাথে আবদ্ধ ভর রৈখিকভাবে বৃদ্ধি পায় ($M(r) \propto r$) যা কোনো দৃশ্যমান আলো বিকিরণ না করা ডার্ক ম্যাটারের অস্তিত্ব অকাট্যভাবে প্রমাণ করে।</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 17</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>দৃশ্যমান তারামণ্ডলীর বাইরে গ্যালাক্সিকে ঘিরে একটি সুবিশাল অদৃশ্য ডার্ক ম্যাটার হ্যালো (Dark Matter Halo) বিদ্যমান যা অতিরিক্ত মহাকর্ষ বল যোগায়</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4537,7 +4291,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>মহাবিশ্বের আনুমানিক বয়স নির্ণয় (সমস্যা 18)</t>
+          <t>নক্ষত্রের বিবর্তন, কৃষ্ণগহ্বর ও মহাজাগতিক গতিবিদ্যা (Stellar Evolution &amp; Black Holes)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4550,25 +4304,25 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>[সমস্যা 18: মহাবিশ্বের আনুমানিক বয়স নির্ণয়]
-হাবল ধ্রুবক $H_0 = 20\text{ km/s/Mpc}$ হলে হাবল সময়ের সূত্রানুসারে ($t = 1/H_0$) আমাদের মহাবিশ্বের আনুমানিক বয়স কত বিলিয়ন বছর হবে?</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+মহাজাগতিক ডার্ক এনার্জি (Dark Energy) এবং ত্বরান্বিত মহাবিশ্ব (Accelerating Universe): টাইপ-১এ সুপারনোভা পর্যবেক্ষণে কীভাবে ১৯৯৮ সালে আবিষ্কৃত হয় যে মহাবিশ্বের প্রসারণের হার হ্রাস না পেয়ে বরং ক্রমশ ত্বরান্বিত হচ্ছে?</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 18)।</t>
+          <t>আদর্শ মোমবাতি হিসেবে ব্যবহৃত Type-Ia সুপারনোভাগুলোর দূরত্ব পরিমাপ করে পার্লমুটার, স্মিট ও রিস দেখতে পান যে উচ্চ রেডশিফটে এরা স্থির গতিতে প্রসারিত মহাবিশ্বের চেয়ে অনেক বেশি দূরে অবস্থিত। এর অর্থ হলো মহাকর্ষীয় আকর্ষণে মহাবিশ্বের প্রসারণ ধীর হওয়ার পরিবর্তে ডার্ক এনার্জির মহাজাগতিক বিকর্ষণ চাপে মহাবিশ্বের প্রসারণ ক্রমেই ত্বরান্বিত হচ্ছে, যার জন্য ২০১১ সালে পদার্থবিজ্ঞানে নোবেল পুরস্কার প্রদান করা হয়।</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 18</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>দূরবর্তী টাইপ-১এ সুপারনোভা প্রত্যাশিত উজ্জ্বলতার চেয়ে ক্ষীণতর পাওয়া যায়, যা মহাজাগতিক ঋণাত্মক চাপযুক্ত ডার্ক এনার্জি দ্বারা স্থানকালের সম্প্রসারণের ত্বরণ নির্দেশ করে</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4588,38 +4342,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>নক্ষত্রের লাল সরণ ও ডপলার প্রভাব (সমস্যা 19)</t>
+          <t>নক্ষত্রের বিবর্তন, কৃষ্ণগহ্বর ও মহাজাগতিক গতিবিদ্যা (Stellar Evolution &amp; Black Holes)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>[সমস্যা 19: নক্ষত্রের লাল সরণ ও ডপলার প্রভাব]
-একটি দূরবর্তী কোয়াসার হতে আগত হাইড্রোজেন $\text{H}_\alpha$ বর্ণালী রেখার প্রকৃত তরঙ্গদৈর্ঘ্য $6563\text{ \AA}$ কিন্তু পৃথিবীতে পরিমাপকৃত মান $4000\text{ \AA}$। কোয়াসারটির লাল সরণ ($z = \Delta\lambda / \lambda$) কত?</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি ব্ল্যাক হোলের টাইডাল বল বা স্প্যাগেটিফিকেশন (Spaghettification): একটি $2.0\text{ m}$ উচ্চতার নভোচারী $M = 10 M_\odot$ ভরের স্টেলার ব্ল্যাক হোলের দিকে পা আগে দিয়ে পতনের সময় তার মাথা ও পায়ের মধ্যে সৃষ্ট মহাকর্ষীয় জোয়ারি টান ব্যাখ্যা কর।</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 19)।</t>
+          <t>মহাকর্ষীয় টাইডাল ত্বরণ পার্থক্য $\Delta g = \left|\frac{dg}{dr}\right|\Delta r = \frac{2GM}{r^3}\Delta r$। যেহেতু বল ঘনমূলের ($r^3$) ব্যস্তানুপাতিক, তাই স্টেলার ব্ল্যাক হোলের ঘটনা দিগন্তের নিকটে মাথা ও পায়ের মধ্যে কয়েক হাজার জি ($\text{g}$) সমতুল্য টেনসিল বিকৃতি সৃষ্টি হয় যা যেকোনো বস্তুকে উল্লম্বভাবে ছিন্নভিন্ন করে স্প্যাগেটির ন্যায় দীর্ঘায়িত করে।</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 19</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>দূরত্বের পার্থক্যের কারণে পায়ে প্রযুক্ত মহাকর্ষীয় আকর্ষণ মাথা অপেক্ষা বহুগুণ তীব্র হওয়ায় নভোচারী সরু সুতার মতো প্রসারিত হয়ে যান</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4639,7 +4393,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>মহাজাগতিক পটভূমি বিকিরণ (CMBR) (সমস্যা 20)</t>
+          <t>নক্ষত্রের বিবর্তন, কৃষ্ণগহ্বর ও মহাজাগতিক গতিবিদ্যা (Stellar Evolution &amp; Black Holes)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4652,25 +4406,25 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>[সমস্যা 20: মহাজাগতিক পটভূমি বিকিরণ (CMBR)]
-মহাজাগতিক পটভূমি বিকিরণের বর্তমান তাপমাত্রা $T = 2.76\text{ K}$। ভীনের সূত্র $\lambda_{max} T = 2.898 \times 10^{-3}\text{ m}\cdot\text{K}$ দ্বারা এই বিকিরণের শীর্ষ তরঙ্গদৈর্ঘ্য কোন অঞ্চলে পড়ে হিসাব কর।</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+মহাজাগতিক সময় মাপকাঠি (Cosmic Calendar): যদি মহাবিশ্বের সম্পূর্ণ ১৩.৮ বিলিয়ন বছরের ইতিহাসকে একটি একক ক্যালেন্ডার বছরে (৩৬৫ দিনে) সংকুচিত করা হয়, তবে মানুষের সম্পূর্ণ লিখিত মানব ইতিহাস এই বছরের কত সেকেন্ডের সমতুল্য?</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 20)।</t>
+          <t>১৩.৮ বিলিয়ন বছর $= 365$ দিন হলে প্রতি দিন $\approx 37.8$ মিলিয়ন বছর, প্রতি ঘণ্টা $\approx 1.58$ মিলিয়ন বছর, প্রতি মিনিট $\approx 26300$ বছর এবং প্রতি সেকেন্ড $\approx 438$ বছর। মানুষের সুমেরীয় ও সিন্ধু সভ্যতার ৫০০০ বছরের সম্পূর্ণ লিখিত ইতিহাস এই মহাজাগতিক বছরের ৩১ ডিসেম্বরের মধ্যরাতের শেষ মাত্র ১১.৪ সেকেন্ডে সম্পন্ন হয়।</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 20</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>মানুষের সম্পূর্ণ লিখিত ইতিহাস শেষ দিনের শেষ মাত্র ১০ থেকে ১৫ সেকেন্ডের সমতুল্য ($1\text{ সেকেন্ড} \approx 438\text{ বছর}$)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4690,44 +4444,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>হাবল সূত্র ও গ্যালাক্সির মন্দীভবন বেগ (সমস্যা 21)</t>
+          <t>উন্নত জ্যোতির্বিজ্ঞান সংশ্লেষণ ও মহাজাগতিক ঘটনা (Advanced Astronomy Synthesis)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>##PRESET:expanding-universe[size:medium]##
-[সমস্যা 21: হাবল সূত্র ও গ্যালাক্সির মন্দীভবন বেগ]
-##PRESET:expanding-universe[size:medium]##
-হাবল ধ্রুবকের মান $H_0 = 70\text{ km/s/Mpc}$ হলে আমাদের থেকে $d = 800\text{ Mpc}$ দূরে অবস্থিত একটি সর্পিলাকার গ্যালাক্সির অপসরণ বেগ (Recession velocity, $v = H_0 d$) কত?</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি তারার পৃষ্ঠ তাপমাত্রা $T = 12000\text{ K}$ এবং ব্যাসার্ধ সূর্যের ব্যাসার্ধের অর্ধেক ($R = 0.5 R_\odot$)। সূর্যের পৃষ্ঠ তাপমাত্রা $5800\text{ K}$ হলে তারাটির মোট উজ্জ্বলতা সূর্যের কত গুণ?</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>##PRESET:expanding-universe[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 21)।</t>
+          <t>$L \propto R^2 T^4 \implies \frac{L}{L_\odot} = \left(\frac{R}{R_\odot}\right)^2 \left(\frac{T}{T_\odot}\right)^4 = (0.5)^2 \times \left(\frac{12000}{5800}\right)^4 = 0.25 \times (2.06896)^4 = 0.25 \times 18.307 \approx 4.577 L_\odot$।</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 21</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>উজ্জ্বলতা $L = 4.57 L_\odot$</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4747,12 +4495,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>কৃষ্ণগহ্বরের সোয়ার্জশিল্ড ব্যাসার্ধ (সমস্যা 22)</t>
+          <t>উন্নত জ্যোতির্বিজ্ঞান সংশ্লেষণ ও মহাজাগতিক ঘটনা (Advanced Astronomy Synthesis)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -4760,31 +4508,25 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>##PRESET:black-hole-event-horizon[size:medium]##
-[সমস্যা 22: কৃষ্ণগহ্বরের সোয়ার্জশিল্ড ব্যাসার্ধ]
-##PRESET:black-hole-event-horizon[size:medium]##
-সূর্যের ভরের 10 গুণ ভরবিশিষ্ট একটি মৃত নক্ষত্র সংকুচিত হয়ে ব্ল্যাকহোলে পরিণত হলে এর ঘটনা দিগন্তের সোয়ার্জশিল্ড ব্যাসার্ধ ($R_s = \frac{2GM}{c^2}$) কত কিলোমিটার হবে? ($M_\odot = 2.0 \times 10^{30}\text{ kg}$)</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি নক্ষত্রের দূরত্বের কারণে এর আপাত মান $m = +12.0$ এবং এর পরম মান $M = +2.0$। নক্ষত্রটির দূরত্ব কত পারসেক?</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>##PRESET:black-hole-event-horizon[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 22)।</t>
+          <t>$m - M = 12.0 - 2.0 = 10.0$। $5\log_{10}(d) - 5 = 10.0 \implies 5\log_{10}(d) = 15.0 \implies \log_{10}(d) = 3.0 \implies d = 10^3 = 1000.0\text{ pc} = 1.0\text{ kpc}$।</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 22</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>দূরত্ব $d = 1000.0\text{ pc} = 1.0\text{ kpc} = 3260.0\text{ ly}$</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4804,38 +4546,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>নাক্ষত্রিক প্যারালাক্স ও পারসেক দূরত্ব (সমস্যা 23)</t>
+          <t>উন্নত জ্যোতির্বিজ্ঞান সংশ্লেষণ ও মহাজাগতিক ঘটনা (Advanced Astronomy Synthesis)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>[সমস্যা 23: নাক্ষত্রিক প্যারালাক্স ও পারসেক দূরত্ব]
-একটি দূরবর্তী নক্ষত্রের বার্ষিক প্যারালাক্স কোণ $p = 0.012''$ (আর্কসেকেন্ড)। নক্ষত্রটির দূরত্ব পারসেক (pc) এবং আলোকবর্ষে (ly) কত হবে? ($d = 1/p$)</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+পৃথিবীর কক্ষপথের গড় ব্যাসার্ধ $1.0\text{ AU} = 1.496 	imes 10^{11}\text{ m}$। সূর্য হতে আলো পৃথিবীতে পৌঁছাতে কত মিনিট কত সেকেন্ড সময় নেয়?</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 23)।</t>
+          <t>সময় $t = \frac{d}{c} = \frac{1.496 \times 10^{11}\text{ m}}{3.0 \times 10^8\text{ m/s}} \approx 498.67\text{ s}$। মিনিটে: $\frac{498.67}{60} = 8\text{ মিনিট } 18.67\text{ সেকেন্ড} \approx 8\text{ মিনিট } 19\text{ সেকেন্ড}$।</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 23</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>সময় $t = 8\text{ মিনিট } 19\text{ সেকেন্ড} = 498.7\text{ s}$</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4855,12 +4597,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>নক্ষত্রের উজ্জ্বলতা ও বিপরীত বর্গীয় সূত্র (সমস্যা 24)</t>
+          <t>উন্নত জ্যোতির্বিজ্ঞান সংশ্লেষণ ও মহাজাগতিক ঘটনা (Advanced Astronomy Synthesis)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -4868,25 +4610,25 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>[সমস্যা 24: নক্ষত্রের উজ্জ্বলতা ও বিপরীত বর্গীয় সূত্র]
-একটি নক্ষত্রের ঔজ্জ্বল্য পৃথিবীর সাপেক্ষে পরিমাপ করা হলো। যদি নক্ষত্রটির দূরত্ব 2 গুণ বৃদ্ধি পায়, তবে পৃথিবীতে এর আপাত উজ্জ্বলতা কত গুণ হ্রাস পাবে?</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি তারা হতে নিঃসৃত আলোর সর্বোচ্চ তীব্রতার তরঙ্গদৈর্ঘ্য $\lambda_{\max} = 725\text{ nm}$ (লাল তারা)। তারাটির পৃষ্ঠের তাপমাত্রা কত?</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 24)।</t>
+          <t>ভীনের সূত্র: $T = \frac{b}{\lambda_{\max}} = \frac{2.898 \times 10^{-3}\text{ m}\cdot\text{K}}{725 \times 10^{-9}\text{ m}} \approx 3997.24\text{ K} \approx 4000.0\text{ K}$।</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 24</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+          <t>পৃষ্ঠ তাপমাত্রা $T = 3997.2\text{ K} \approx 4000.0\text{ K}$</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4906,38 +4648,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ভীনের সরণ সূত্র ও নক্ষত্রের পৃষ্ঠ তাপমাত্রা (সমস্যা 25)</t>
+          <t>উন্নত জ্যোতির্বিজ্ঞান সংশ্লেষণ ও মহাজাগতিক ঘটনা (Advanced Astronomy Synthesis)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>[সমস্যা 25: ভীনের সরণ সূত্র ও নক্ষত্রের পৃষ্ঠ তাপমাত্রা]
-সূর্যের বিকিরণ বর্ণালীতে সর্বোচ্চ তীব্রতার তরঙ্গদৈর্ঘ্য $\lambda_{max} = 5000\text{ \AA}$। অন্য একটি নক্ষত্রের সর্বোচ্চ তীব্রতার তরঙ্গদৈর্ঘ্য $4000\text{ \AA}$ হলে নক্ষত্রটির পৃষ্ঠের তাপমাত্রা কত? (সূর্যের তাপমাত্রা $6000\text{ K}$)</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি গ্যালাক্সির দূরত্ব $d = 200\text{ Mpc}$ হলে হাবলের সূত্রানুযায়ী এর অপসরণ দ্রুতি কত? ($H_0 = 70\text{ km/s/Mpc}$)।</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 25)।</t>
+          <t>হাবলের সূত্র: $v = H_0 d = (70\text{ km/s/Mpc}) \times 200\text{ Mpc} = 14000.0\text{ km/s}$।</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 25</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+          <t>অপসরণ দ্রুতি $v = 14000.0\text{ km/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4957,12 +4699,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>স্টিফান-বোল্টজম্যান সূত্র ও নক্ষত্রের দীপ্তি (সমস্যা 26)</t>
+          <t>উন্নত জ্যোতির্বিজ্ঞান সংশ্লেষণ ও মহাজাগতিক ঘটনা (Advanced Astronomy Synthesis)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -4970,25 +4712,25 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>[সমস্যা 26: স্টিফান-বোল্টজম্যান সূত্র ও নক্ষত্রের দীপ্তি]
-একটি নক্ষত্রের ব্যাসার্ধ সূর্যের ব্যাসার্ধের দ্বিগুণ এবং পৃষ্ঠের তাপমাত্রা সূর্যের তাপমাত্রার 6 গুণ। নক্ষত্রটির সামগ্রিক দীপ্তি (Luminosity) সূর্যের তুলনায় কত গুণ হবে? ($L \propto R^2 T^4$)</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+মহাবিশ্বের ভর-শক্তির উপাদান: আধুনিক প্ল্যাঙ্ক স্যাটেলাইট পর্যবেক্ষণ অনুসারে সাধারণ দৃশ্যমান পদার্থ, ডার্ক ম্যাটার এবং ডার্ক এনার্জির শতকরা অনুপাত কত?</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 26)।</t>
+          <t>মহাবিশ্বের মোট ক্রিটিক্যাল ঘনত্বের মাত্র প্রায় ৪.৯% গঠিত পরিচিত পরমাণু ও গ্যাস দ্বারা (Baryonic matter)। প্রায় ২৬.৮% হলো শীতল ডার্ক ম্যাটার যা আলো বিকিরণ না করে গ্যালাক্সিকে মহাকর্ষীয়ভাবে ধরে রাখে। অবশিষ্ট প্রায় ৬৮.৩% হলো ডার্ক এনার্জি যা মহাজাগতিক স্থানকালের ত্বরান্বিত প্রসারণ নিয়ন্ত্রণ করছে।</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 26</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+          <t>সাধারণ পদার্থ $\approx 4.9\%$, ডার্ক ম্যাটার $\approx 26.8\%$, ডার্ক এনার্জি $\approx 68.3\%$</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5008,38 +4750,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>চন্দ্রশেখর সীমা ও শ্বেত বামন নক্ষত্র (সমস্যা 27)</t>
+          <t>উন্নত জ্যোতির্বিজ্ঞান সংশ্লেষণ ও মহাজাগতিক ঘটনা (Advanced Astronomy Synthesis)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>[সমস্যা 27: চন্দ্রশেখর সীমা ও শ্বেত বামন নক্ষত্র]
-সূর্যের ভরের ১.৪ গুণ ভর ($1.4 M_\odot$) চন্দ্রশেখর সীমা নামে পরিচিত। $M = 8.0 M_\odot$ ভরের একটি নক্ষত্রের মৃত্যুর পর এর সম্ভাব্য রূপ কী হবে—শ্বেত বামন, নিউট্রন স্টার না ব্ল্যাকহোল?</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি সুপারনোভার পরম মান $M = -19.3$। এটি যদি এমন এক দূরত্বে বিস্ফোরিত হয় যার ফলে এর আপাত মান $m = +5.7$ হয়, তবে সুপারনোভাটি কত মেগাপারসেক দূরে অবস্থিত?</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 27)।</t>
+          <t>$m - M = 5.7 - (-19.3) = 25.0$। $5\log_{10}(d) - 5 = 25.0 \implies 5\log_{10}(d) = 30.0 \implies \log_{10}(d) = 6.0 \implies d = 10^6\text{ pc} = 1.0\text{ Mpc} \times 100 = 100.0\text{ Mpc}$।</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 27</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+          <t>দূরত্ব $d = 100.0\text{ Mpc}$</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5059,12 +4801,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>মহাবিশ্বের আনুমানিক বয়স নির্ণয় (সমস্যা 28)</t>
+          <t>উন্নত জ্যোতির্বিজ্ঞান সংশ্লেষণ ও মহাজাগতিক ঘটনা (Advanced Astronomy Synthesis)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -5072,25 +4814,25 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>[সমস্যা 28: মহাবিশ্বের আনুমানিক বয়স নির্ণয়]
-হাবল ধ্রুবক $H_0 = 100\text{ km/s/Mpc}$ হলে হাবল সময়ের সূত্রানুসারে ($t = 1/H_0$) আমাদের মহাবিশ্বের আনুমানিক বয়স কত বিলিয়ন বছর হবে?</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি নক্ষত্রের ভর $M = 3.0 M_\odot$ হলে এর ব্যাসার্ধ সংকুচিত হয়ে ব্ল্যাক হোলে রূপান্তরের জন্য সংকট সোয়ার্জশিল্ড ব্যাসার্ধ কত কিমি হতে হবে?</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 28)।</t>
+          <t>$R_s = 3 \times R_s(\text{Sun}) = 3 \times 2.966\text{ km} \approx 8.898\text{ km} \approx 8.90\text{ km}$।</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 28</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+          <t>সোয়ার্জশিল্ড ব্যাসার্ধ $R_s = 8.90\text{ km}$</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5110,38 +4852,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>নক্ষত্রের লাল সরণ ও ডপলার প্রভাব (সমস্যা 29)</t>
+          <t>উন্নত জ্যোতির্বিজ্ঞান সংশ্লেষণ ও মহাজাগতিক ঘটনা (Advanced Astronomy Synthesis)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>[সমস্যা 29: নক্ষত্রের লাল সরণ ও ডপলার প্রভাব]
-একটি দূরবর্তী কোয়াসার হতে আগত হাইড্রোজেন $\text{H}_\alpha$ বর্ণালী রেখার প্রকৃত তরঙ্গদৈর্ঘ্য $6563\text{ \AA}$ কিন্তু পৃথিবীতে পরিমাপকৃত মান $12000\text{ \AA}$। কোয়াসারটির লাল সরণ ($z = \Delta\lambda / \lambda$) কত?</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+মহাজাগতিক স্কেলে মহাকর্ষীয় লেন্সিং (Gravitational Lensing) কীভাবে আইনস্টাইনের সাধারণ আপেক্ষিকতা তত্ত্বকে প্রমাণ করে?</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 29)।</t>
+          <t>আইনস্টাইনের সাধারণ আপেক্ষিকতা অনুযায়ী ভর স্থানকালকে বাঁকায়। দূরবর্তী কোয়েসার হতে আগত আলোকরশ্মি মধ্যবর্তী কোনো ভারী গ্যালাক্সির পাশ দিয়ে আসার সময় বাঁকানো স্থানকাল অনুসরণ করে বিচ্যুত হয়। ফলে পর্যবেক্ষকের কাছে একই বস্তুর একাধিক প্রতিবিম্ব, চাপ বা সম্পূর্ণ বৃত্তাকার 'আইনস্টাইন রিং' দৃশ্যমান হয়, যা স্থানকালের বক্রতার প্রত্যক্ষ প্রমাণ।</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 29</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+          <t>বিশাল ভরের গ্যালাক্সি বা গ্যালাক্সি ক্লাস্টার স্থানকালকে বাঁকিয়ে দিয়ে দূরবর্তী বস্তুর আলোকে লেন্সের ন্যায় কেন্দ্রীভূত করে একাধিক প্রতিবিম্ব বা আইনস্টাইন রিং গঠন করে</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5161,12 +4903,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>মহাজাগতিক পটভূমি বিকিরণ (CMBR) (সমস্যা 30)</t>
+          <t>উন্নত জ্যোতির্বিজ্ঞান সংশ্লেষণ ও মহাজাগতিক ঘটনা (Advanced Astronomy Synthesis)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -5174,25 +4916,25 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>[সমস্যা 30: মহাজাগতিক পটভূমি বিকিরণ (CMBR)]
-মহাজাগতিক পটভূমি বিকিরণের বর্তমান তাপমাত্রা $T = 2.72\text{ K}$। ভীনের সূত্র $\lambda_{max} T = 2.898 \times 10^{-3}\text{ m}\cdot\text{K}$ দ্বারা এই বিকিরণের শীর্ষ তরঙ্গদৈর্ঘ্য কোন অঞ্চলে পড়ে হিসাব কর।</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+ফার্মি প্যারাডক্স (Fermi Paradox): 'মহাবিশ্ব যদি এতই প্রাচীন এবং বিলিয়ন বিলিয়ন নক্ষত্রজগৎ বিশিষ্ট হয়, তবে বুদ্ধিমান বহির্জাগতিক প্রাণীরা কোথায়?'—এই প্যারাডক্সের মূল বৈজ্ঞানিক তাৎপর্য কী?</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 30)।</t>
+          <t>পদার্থবিজ্ঞানী এনরিকো ফার্মি ১৯৫০ সালে প্রশ্ন করেন যে গ্যালাক্সির বয়স ১০ বিলিয়ন বছর হওয়ায় যেকোনো সভ্যতার মহাকাশ ভ্রমণের জন্য কয়েক মিলিয়ন বছরই যথেষ্ট ছিল। কোনো এলিয়েন সভ্যতার প্রমাণ না পাওয়ার ব্যাখ্যায় বিজ্ঞানীরা 'গ্রেট ফিল্টার' (Great Filter), সভ্যতার স্ব-ধ্বংস বা বিরল পৃথিবী প্রকল্পকে বিবেচনা করেন।</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 30</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+          <t>ড্রেক সমীকরণ অনুসারে অসংখ্য প্রযুক্তিগত সভ্যতার সম্ভাবনা থাকা সত্ত্বেও কোনো বেতার সংকেত বা সাক্ষ্যের অনুপস্থিতি নির্দেশ করে যে মহাবিশ্বে উন্নত সভ্যতার আয়ুষ্কাল অতি সংক্ষিপ্ত অথবা বুদ্ধিমান প্রাণের উদ্ভব অত্যন্ত বিরল</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5212,44 +4954,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>হাবল সূত্র ও গ্যালাক্সির মন্দীভবন বেগ (সমস্যা 31)</t>
+          <t>উন্নত জ্যোতির্বিজ্ঞান সংশ্লেষণ ও মহাজাগতিক ঘটনা (Advanced Astronomy Synthesis)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>##PRESET:expanding-universe[size:medium]##
-[সমস্যা 31: হাবল সূত্র ও গ্যালাক্সির মন্দীভবন বেগ]
-##PRESET:expanding-universe[size:medium]##
-হাবল ধ্রুবকের মান $H_0 = 70\text{ km/s/Mpc}$ হলে আমাদের থেকে $d = 400\text{ Mpc}$ দূরে অবস্থিত একটি সর্পিলাকার গ্যালাক্সির অপসরণ বেগ (Recession velocity, $v = H_0 d$) কত?</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি তারা প্রতি সেকেন্ডে $4.0 	imes 10^{26}\text{ J}$ শক্তি বিকিরণ করে। তারাটির পৃষ্ঠ তাপমাত্রা $8000\text{ K}$ হলে এর ব্যাসার্ধ কত কিলোমিটার? ($\sigma = 5.67 \times 10^{-8}\text{ W/m}^2\cdot\text{K}^4$)।</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>##PRESET:expanding-universe[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 31)।</t>
+          <t>$L = 4\pi R^2 \sigma T^4 \implies R = \sqrt{\frac{L}{4\pi\sigma T^4}} = \sqrt{\frac{4.0 \times 10^{26}}{4\pi (5.67 \times 10^{-8})(8000)^4}} = \sqrt{\frac{4.0 \times 10^{26}}{1.261 \times 10^{-6} \times 4.096 \times 10^{15}}} = \sqrt{\frac{4.0 \times 10^{26}}{2.923 \times 10^{9}}} = \sqrt{1.368 \times 10^{17}} \approx 1.1698 \times 10^9\text{ m} \approx 1.17 \times 10^6\text{ km}$।</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 31</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>ব্যাসার্ধ $R = 1.17 \times 10^6\text{ km}$</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5269,12 +5005,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>কৃষ্ণগহ্বরের সোয়ার্জশিল্ড ব্যাসার্ধ (সমস্যা 32)</t>
+          <t>উন্নত জ্যোতির্বিজ্ঞান সংশ্লেষণ ও মহাজাগতিক ঘটনা (Advanced Astronomy Synthesis)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -5282,31 +5018,25 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>##PRESET:black-hole-event-horizon[size:medium]##
-[সমস্যা 32: কৃষ্ণগহ্বরের সোয়ার্জশিল্ড ব্যাসার্ধ]
-##PRESET:black-hole-event-horizon[size:medium]##
-সূর্যের ভরের 6 গুণ ভরবিশিষ্ট একটি মৃত নক্ষত্র সংকুচিত হয়ে ব্ল্যাকহোলে পরিণত হলে এর ঘটনা দিগন্তের সোয়ার্জশিল্ড ব্যাসার্ধ ($R_s = \frac{2GM}{c^2}$) কত কিলোমিটার হবে? ($M_\odot = 2.0 \times 10^{30}\text{ kg}$)</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+দুটি তারার আপাত উজ্জ্বলতার অনুপাত $F_1 / F_2 = 10000$ হলে তাদের আপাত মানের পার্থক্য কত?</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>##PRESET:black-hole-event-horizon[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 32)।</t>
+          <t>$m_2 - m_1 = 2.5 \log_{10}(10000) = 2.5(4) = 10.0$।</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 32</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+          <t>পার্থক্য $m_2 - m_1 = 10.0$ মান</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5326,38 +5056,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>নাক্ষত্রিক প্যারালাক্স ও পারসেক দূরত্ব (সমস্যা 33)</t>
+          <t>উন্নত জ্যোতির্বিজ্ঞান সংশ্লেষণ ও মহাজাগতিক ঘটনা (Advanced Astronomy Synthesis)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>[সমস্যা 33: নাক্ষত্রিক প্যারালাক্স ও পারসেক দূরত্ব]
-একটি দূরবর্তী নক্ষত্রের বার্ষিক প্যারালাক্স কোণ $p = 0.08''$ (আর্কসেকেন্ড)। নক্ষত্রটির দূরত্ব পারসেক (pc) এবং আলোকবর্ষে (ly) কত হবে? ($d = 1/p$)</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি নক্ষত্রের ব্যাসার্ধ সূর্যের সমান কিন্তু পৃষ্ঠের তাপমাত্রা সূর্যের তিনগুণ ($T = 3 T_\odot$)। নক্ষত্রটির দীপ্তি সূর্যের দীপ্তির কত গুণ?</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 33)।</t>
+          <t>$L \propto T^4 \implies \frac{L}{L_\odot} = 3^4 = 81.0$।</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 33</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+          <t>দীপ্তি $L = 81.0 L_\odot$</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5377,12 +5107,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>নক্ষত্রের উজ্জ্বলতা ও বিপরীত বর্গীয় সূত্র (সমস্যা 34)</t>
+          <t>উন্নত জ্যোতির্বিজ্ঞান সংশ্লেষণ ও মহাজাগতিক ঘটনা (Advanced Astronomy Synthesis)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -5390,25 +5120,25 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>[সমস্যা 34: নক্ষত্রের উজ্জ্বলতা ও বিপরীত বর্গীয় সূত্র]
-একটি নক্ষত্রের ঔজ্জ্বল্য পৃথিবীর সাপেক্ষে পরিমাপ করা হলো। যদি নক্ষত্রটির দূরত্ব 10 গুণ বৃদ্ধি পায়, তবে পৃথিবীতে এর আপাত উজ্জ্বলতা কত গুণ হ্রাস পাবে?</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি ব্ল্যাক হোলের ব্যাসার্ধ $R_s = 60.0\text{ km}$ হলে এর ভর কতটি সৌর ভরের সমান?</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 34)।</t>
+          <t>প্রতি সৌর ভরের জন্য $R_s \approx 2.966\text{ km}$। ফলে ভর $M = \frac{60.0}{2.966} M_\odot \approx 20.23 M_\odot$।</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 34</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>ভর $M \approx 20.23 M_\odot \approx 20.2\text{ সৌর ভর}$</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5428,38 +5158,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ভীনের সরণ সূত্র ও নক্ষত্রের পৃষ্ঠ তাপমাত্রা (সমস্যা 35)</t>
+          <t>উন্নত জ্যোতির্বিজ্ঞান সংশ্লেষণ ও মহাজাগতিক ঘটনা (Advanced Astronomy Synthesis)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>[সমস্যা 35: ভীনের সরণ সূত্র ও নক্ষত্রের পৃষ্ঠ তাপমাত্রা]
-সূর্যের বিকিরণ বর্ণালীতে সর্বোচ্চ তীব্রতার তরঙ্গদৈর্ঘ্য $\lambda_{max} = 5000\text{ \AA}$। অন্য একটি নক্ষত্রের সর্বোচ্চ তীব্রতার তরঙ্গদৈর্ঘ্য $12000\text{ \AA}$ হলে নক্ষত্রটির পৃষ্ঠের তাপমাত্রা কত? (সূর্যের তাপমাত্রা $6000\text{ K}$)</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি তারার প্যারালাক্স কোণ $p = 0.05\text{ arcsec}$ হলে তারাটির দূরত্ব কত পারসেক এবং কত আলোকবর্ষ?</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 35)।</t>
+          <t>$d = \frac{1}{0.05} = 20.0\text{ pc}$। আলোকবর্ষে: $d = 20 \times 3.26 = 65.2\text{ ly}$।</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 35</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>দূরত্ব $d = 20.0\text{ pc} = 65.2\text{ ly}$</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5479,12 +5209,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>স্টিফান-বোল্টজম্যান সূত্র ও নক্ষত্রের দীপ্তি (সমস্যা 36)</t>
+          <t>উন্নত জ্যোতির্বিজ্ঞান সংশ্লেষণ ও মহাজাগতিক ঘটনা (Advanced Astronomy Synthesis)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -5492,25 +5222,25 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>[সমস্যা 36: স্টিফান-বোল্টজম্যান সূত্র ও নক্ষত্রের দীপ্তি]
-একটি নক্ষত্রের ব্যাসার্ধ সূর্যের ব্যাসার্ধের দ্বিগুণ এবং পৃষ্ঠের তাপমাত্রা সূর্যের তাপমাত্রার 2 গুণ। নক্ষত্রটির সামগ্রিক দীপ্তি (Luminosity) সূর্যের তুলনায় কত গুণ হবে? ($L \propto R^2 T^4$)</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+মহাজাগতিক সম্প্রসারণে স্থানকালের প্রসার: গ্যালাক্সিগুলো কি মহাশূন্যের ভেতর দিয়ে গতিশীল নাকি মহাজাগতিক স্থানকাল নিজেই প্রসারিত হচ্ছে?</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 36)।</t>
+          <t>সাধারণ আপেক্ষিকতা অনুসারে গ্যালাক্সিগুলো কোনো স্থির মঞ্চে গতির মাধ্যমে দূরে সরছে না; বরং গ্যালাক্সিগুলোর মধ্যবর্তী স্থানকালিক কাঠামো নিজেই স্ফীত হচ্ছে (যেমন একটি বেলুন ফোলানোর সময় তার পৃষ্ঠের বিন্দুগুলোর পরস্পর হতে দূরে সরে যাওয়া)। ফলে কোনো গ্যালাক্সি আলোর চেয়েও দ্রুত অপসৃত হতে পারে যা বিশেষ আপেক্ষিকতাকে লঙ্ঘন করে না কারণ কোনো বস্তু স্থানকালের সাপেক্ষে আলো অপেক্ষা দ্রুত চলছে না।</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 36</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>মহাবিশ্বের স্থানকাল (Fabric of spacetime) নিজেই সমসত্ত্বভাবে প্রসারিত হচ্ছে, যার ফলে গ্যালাক্সিগুলোর মধ্যকার পারস্পরিক দূরত্ব বৃদ্ধি পায়</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5530,38 +5260,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>চন্দ্রশেখর সীমা ও শ্বেত বামন নক্ষত্র (সমস্যা 37)</t>
+          <t>উন্নত জ্যোতির্বিজ্ঞান সংশ্লেষণ ও মহাজাগতিক ঘটনা (Advanced Astronomy Synthesis)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>[সমস্যা 37: চন্দ্রশেখর সীমা ও শ্বেত বামন নক্ষত্র]
-সূর্যের ভরের ১.৪ গুণ ভর ($1.4 M_\odot$) চন্দ্রশেখর সীমা নামে পরিচিত। $M = 4.0 M_\odot$ ভরের একটি নক্ষত্রের মৃত্যুর পর এর সম্ভাব্য রূপ কী হবে—শ্বেত বামন, নিউট্রন স্টার না ব্ল্যাকহোল?</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি তারার পরম উজ্জ্বলতা $M = 4.83$ (সূর্যের পরম মান)। তারাটি যদি $10\text{ pc}$ দূরত্বে অবস্থান করে, তবে এর আপাত মান $m$ কত হবে?</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 37)।</t>
+          <t>সংজ্ঞানুযায়ী $10\text{ pc}$ দূরত্বে কোনো তারার আপাত মানই তার পরম মানের সমান: $m - M = 5\log_{10}(10) - 5 = 5(1) - 5 = 0 \implies m = M = +4.83$।</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 37</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>আপাত মান $m = +4.83$</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5581,12 +5311,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>মহাবিশ্বের আনুমানিক বয়স নির্ণয় (সমস্যা 38)</t>
+          <t>উন্নত জ্যোতির্বিজ্ঞান সংশ্লেষণ ও মহাজাগতিক ঘটনা (Advanced Astronomy Synthesis)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -5594,25 +5324,25 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>[সমস্যা 38: মহাবিশ্বের আনুমানিক বয়স নির্ণয়]
-হাবল ধ্রুবক $H_0 = 60\text{ km/s/Mpc}$ হলে হাবল সময়ের সূত্রানুসারে ($t = 1/H_0$) আমাদের মহাবিশ্বের আনুমানিক বয়স কত বিলিয়ন বছর হবে?</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি রেডিও গ্যালাক্সি হতে আগত সংকেতের কম্পাঙ্ক প্রকৃত কম্পাঙ্কের $90\%$ পরিমাপ করা হলো। গ্যালাক্সিটির অপসরণ দ্রুতি কত? ($c = 3.0 \times 10^8\text{ m/s}$)।</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 38)।</t>
+          <t>ডপলার কম্পাঙ্ক: $\frac{f'}{f} = \sqrt{\frac{1 - v/c}{1 + v/c}} = 0.90$। বর্গ করে: $\frac{1 - v/c}{1 + v/c} = 0.81 \implies 1 - v/c = 0.81 + 0.81 v/c \implies 1.81 v/c = 0.19 \implies v/c = \frac{0.19}{1.81} \approx 0.10497 \implies v \approx 3.149 \times 10^7\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 38</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>অপসরণ দ্রুতি $v = 3.16 \times 10^7\text{ m/s} \approx 0.105 c$</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5632,38 +5362,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>নক্ষত্রের লাল সরণ ও ডপলার প্রভাব (সমস্যা 39)</t>
+          <t>উন্নত জ্যোতির্বিজ্ঞান সংশ্লেষণ ও মহাজাগতিক ঘটনা (Advanced Astronomy Synthesis)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>[সমস্যা 39: নক্ষত্রের লাল সরণ ও ডপলার প্রভাব]
-একটি দূরবর্তী কোয়াসার হতে আগত হাইড্রোজেন $\text{H}_\alpha$ বর্ণালী রেখার প্রকৃত তরঙ্গদৈর্ঘ্য $6563\text{ \AA}$ কিন্তু পৃথিবীতে পরিমাপকৃত মান $8000\text{ \AA}$। কোয়াসারটির লাল সরণ ($z = \Delta\lambda / \lambda$) কত?</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি হোয়াইট ডোয়ার্ফ নক্ষত্রের তাপমাত্রা $T = 24000\text{ K}$ হলে এর বিকিরণ শিখরের তরঙ্গদৈর্ঘ্য কত ন্যানোমিটার?</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 39)।</t>
+          <t>ভীনের সূত্র: $\lambda_{\max} = \frac{b}{T} = \frac{2.898 \times 10^{-3}\text{ m}\cdot\text{K}}{24000\text{ K}} \approx 1.2075 \times 10^{-7}\text{ m} = 120.75\text{ nm}$।</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 39</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+          <t>তরঙ্গদৈর্ঘ্য $\lambda_{\max} = 120.75\text{ nm}$ (অতিবেগুনী অঞ্চল)</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5683,12 +5413,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>মহাজাগতিক পটভূমি বিকিরণ (CMBR) (সমস্যা 40)</t>
+          <t>উন্নত জ্যোতির্বিজ্ঞান সংশ্লেষণ ও মহাজাগতিক ঘটনা (Advanced Astronomy Synthesis)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -5696,25 +5426,25 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>[সমস্যা 40: মহাজাগতিক পটভূমি বিকিরণ (CMBR)]
-মহাজাগতিক পটভূমি বিকিরণের বর্তমান তাপমাত্রা $T = 2.710\text{ K}$। ভীনের সূত্র $\lambda_{max} T = 2.898 \times 10^{-3}\text{ m}\cdot\text{K}$ দ্বারা এই বিকিরণের শীর্ষ তরঙ্গদৈর্ঘ্য কোন অঞ্চলে পড়ে হিসাব কর।</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+হকিং বিকিরণ (Hawking Radiation): কোয়ান্টাম ক্ষেত্র তত্ত্ব অনুসারে কৃষ্ণগহ্বর কি সম্পূর্ণ চিরস্থায়ী? কৃষ্ণগহ্বরের বাষ্পীভবন ও আয়ুষ্কাল ধারণাটি ব্যাখ্যা কর।</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 40)।</t>
+          <t>স্টিফেন হকিং ১৯৭৪ সালে দেখান যে কোয়ান্টাম ভ্যাকুয়াম ফ্ল্যাকচুয়েশনের ফলে দিগন্তের মুখে কণা-প্রতিকণা জোড় তৈরি হলে ঋণাত্মক শক্তির কণা কৃষ্ণগহ্বরে প্রবেশ করে এবং ধনাত্মক শক্তির কণা বিকিরণ হিসেবে অসীমে পালিয়ে যায়। ফলে কৃষ্ণগহ্বরের কার্যকর ভর হ্রাস পেতে থাকে ($dM/dt \propto -1/M^2$)। সৌর ভরের ব্ল্যাক হোলের জন্য এই আয়ুষ্কাল প্রায় $10^{67}$ বছর, তবে অতিক্ষুদ্র প্রাইমরডিয়াল ব্ল্যাক হোল দ্রুত বাষ্পীভূত হয়ে গামা বিস্ফোরণে মিলিয়ে যেতে পারে।</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 40</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+          <t>ঘটনা দিগন্তের সন্নিকটে ভার্চুয়াল কণা-প্রতিকণা জোড় সৃষ্টির ফলে কৃষ্ণগহ্বর অত্যন্ত ধীরগতিতে শক্তি বিকিরণ করে ভর হারিয়ে চূড়ান্তভাবে বাষ্পীভূত হয়ে বিলুপ্ত হয়</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5734,44 +5464,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>হাবল সূত্র ও গ্যালাক্সির মন্দীভবন বেগ (সমস্যা 41)</t>
+          <t>পর্যবেক্ষণমূলক জ্যোতির্ভৌতবিদ্যা, যুগল নক্ষত্র ও আপেক্ষিক মহাজাগতিক বিজ্ঞান (Astrophysics &amp; Binary Stars)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>##PRESET:expanding-universe[size:medium]##
-[সমস্যা 41: হাবল সূত্র ও গ্যালাক্সির মন্দীভবন বেগ]
-##PRESET:expanding-universe[size:medium]##
-হাবল ধ্রুবকের মান $H_0 = 70\text{ km/s/Mpc}$ হলে আমাদের থেকে $d = 1200\text{ Mpc}$ দূরে অবস্থিত একটি সর্পিলাকার গ্যালাক্সির অপসরণ বেগ (Recession velocity, $v = H_0 d$) কত?</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি গ্যালাক্সির রেডশিফট $z = 0.15$ পরিমাপ করা হলো। হাবলের সূত্রানুযায়ী ($H_0 = 70.0\text{ km}\cdot\text{s}^{-1}\cdot\text{Mpc}^{-1}$): (ক) গ্যালাক্সিটির অপসরণ দ্রুতি $v$, এবং (খ) পৃথিবী হতে এর দূরত্ব মেগাপারসেক ও আলোকবর্ষে নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>##PRESET:expanding-universe[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 41)।</t>
+          <t>ডপলার বেগ $v = z c = 0.15 \times (3.0 \times 10^5\text{ km/s}) = 45000.0\text{ km/s}$। হাবলের সূত্র: $d = \frac{v}{H_0} = \frac{45000\text{ km/s}}{70.0\text{ km/s/Mpc}} \approx 642.86\text{ Mpc}$। আলোকবর্ষে: $d = 642.86 \times (3.26 \times 10^6\text{ ly}) \approx 2.0957 \times 10^9\text{ ly} \approx 2.10\text{ বিলিয়ন আলোকবর্ষ}$।</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 41</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+          <t>(ক) অপসরণ বেগ $v = 45000.0\text{ km/s}$, (খ) দূরত্ব $d = 642.86\text{ Mpc} = 2.096 \times 10^9\text{ ly}$</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5791,12 +5515,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>কৃষ্ণগহ্বরের সোয়ার্জশিল্ড ব্যাসার্ধ (সমস্যা 42)</t>
+          <t>পর্যবেক্ষণমূলক জ্যোতির্ভৌতবিদ্যা, যুগল নক্ষত্র ও আপেক্ষিক মহাজাগতিক বিজ্ঞান (Astrophysics &amp; Binary Stars)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -5804,31 +5528,25 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>##PRESET:black-hole-event-horizon[size:medium]##
-[সমস্যা 42: কৃষ্ণগহ্বরের সোয়ার্জশিল্ড ব্যাসার্ধ]
-##PRESET:black-hole-event-horizon[size:medium]##
-সূর্যের ভরের 2 গুণ ভরবিশিষ্ট একটি মৃত নক্ষত্র সংকুচিত হয়ে ব্ল্যাকহোলে পরিণত হলে এর ঘটনা দিগন্তের সোয়ার্জশিল্ড ব্যাসার্ধ ($R_s = \frac{2GM}{c^2}$) কত কিলোমিটার হবে? ($M_\odot = 2.0 \times 10^{30}\text{ kg}$)</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+চন্দ্রশেখর সীমা $M = 1.44 M_\odot = 2.88 \times 10^{30}\text{ kg}$ সমমানের ভরের একটি শ্বেত বামনের ব্যাসার্ধ $R = 5000.0\text{ km}$। এর পৃষ্ঠে গড় মহাকর্ষীয় ত্বরণ $g$ এবং গড় ভর ঘনত্ব $\rho$ নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>##PRESET:black-hole-event-horizon[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 42)।</t>
+          <t>পৃষ্ঠ ত্বরণ $g = \frac{G M}{R^2} = \frac{(6.674 \times 10^{-11}) \times (2.88 \times 10^{30})}{(5.0 \times 10^6)^2} = \frac{1.922 \times 10^{20}}{2.5 \times 10^{13}} \approx 7.688 \times 10^6\text{ m/s}^2$। গোলকের আয়তন $V = \frac{4}{3}\pi R^3 = \frac{4}{3}\pi (5.0 \times 10^6)^3 \approx 5.236 \times 10^{20}\text{ m}^3$। গড় ঘনত্ব $\rho = \frac{M}{V} = \frac{2.88 \times 10^{30}}{5.236 \times 10^{20}} \approx 5.50 \times 10^9\text{ kg/m}^3$ (প্রতি ঘন সেন্টিমিটারে ৫.৫ টন)।</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 42</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>পৃষ্ঠ ত্বরণ $g = 7.69 \times 10^6\text{ m/s}^2$, গড় ঘনত্ব $\rho = 5.50 \times 10^9\text{ kg/m}^3$</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5848,38 +5566,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>নাক্ষত্রিক প্যারালাক্স ও পারসেক দূরত্ব (সমস্যা 43)</t>
+          <t>পর্যবেক্ষণমূলক জ্যোতির্ভৌতবিদ্যা, যুগল নক্ষত্র ও আপেক্ষিক মহাজাগতিক বিজ্ঞান (Astrophysics &amp; Binary Stars)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>[সমস্যা 43: নাক্ষত্রিক প্যারালাক্স ও পারসেক দূরত্ব]
-একটি দূরবর্তী নক্ষত্রের বার্ষিক প্যারালাক্স কোণ $p = 0.04''$ (আর্কসেকেন্ড)। নক্ষত্রটির দূরত্ব পারসেক (pc) এবং আলোকবর্ষে (ly) কত হবে? ($d = 1/p$)</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি তারার বার্ষিক প্যারালাক্স লম্বন কোণ $p = 0.025\text{ arcsec}$ এবং দৃশ্যমান আপাত মান $m = +8.5$। তারাটির দূরত্ব পারসেকে এবং পরম মান (Absolute magnitude $M$) নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 43)।</t>
+          <t>দূরত্ব $d = \frac{1}{p} = \frac{1}{0.025} = 40.0\text{ pc}$। দূরত্ব মডিউলাস সূত্র: $m - M = 5\log_{10}(d) - 5 \implies M = m - 5\log_{10}(d) + 5 = 8.5 - 5\log_{10}(40) + 5 = 13.5 - 5(1.60206) = 13.5 - 8.0103 \approx +5.49$।</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 43</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+          <t>দূরত্ব $d = 40.0\text{ pc}$, পরম মান $M = +5.49$</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5899,12 +5617,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>নক্ষত্রের উজ্জ্বলতা ও বিপরীত বর্গীয় সূত্র (সমস্যা 44)</t>
+          <t>পর্যবেক্ষণমূলক জ্যোতির্ভৌতবিদ্যা, যুগল নক্ষত্র ও আপেক্ষিক মহাজাগতিক বিজ্ঞান (Astrophysics &amp; Binary Stars)</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -5912,25 +5630,25 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>[সমস্যা 44: নক্ষত্রের উজ্জ্বলতা ও বিপরীত বর্গীয় সূত্র]
-একটি নক্ষত্রের ঔজ্জ্বল্য পৃথিবীর সাপেক্ষে পরিমাপ করা হলো। যদি নক্ষত্রটির দূরত্ব 6 গুণ বৃদ্ধি পায়, তবে পৃথিবীতে এর আপাত উজ্জ্বলতা কত গুণ হ্রাস পাবে?</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি সুপারম্যাসিভ কৃষ্ণগহ্বরের ভর $M = 1.0 \times 10^8 M_\odot = 2.0 \times 10^{38}\text{ kg}$ হলে এর: (ক) সোয়ার্জশিল্ড ঘটনা দিগন্ত ব্যাসার্ধ $R_s$, এবং (খ) ফোটন গোলক ব্যাসার্ধ $R_{\text{ph}} = 1.5 R_s$ অ্যাস্ট্রোনমিক্যাল ইউনিটে ($	ext{AU}$) নির্ণয় কর। ($1\text{ AU} = 1.496 \times 10^{11}\text{ m}$)।</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 44)।</t>
+          <t>সোয়ার্জশিল্ড ব্যাসার্ধ $R_s = \frac{2 G M}{c^2} = (10^8) \times (2.966\text{ km}) = 2.966 \times 10^8\text{ km} = 2.966 \times 10^{11}\text{ m}$। $\text{AU}$-তে: $R_s = \frac{2.966 \times 10^{11}}{1.496 \times 10^{11}} \approx 1.9826\text{ AU}$। ফোটন গোলকের ব্যাসার্ধ (যেখানে আলো বৃত্তাকার কক্ষপথে ঘোরে) $R_{\text{ph}} = 1.5 R_s = 1.5 \times 1.9826 \approx 2.974\text{ AU}$।</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 44</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+          <t>(ক) $R_s = 2.966 \times 10^8\text{ km} \approx 1.98\text{ AU}$, (খ) $R_{\text{ph}} \approx 2.97\text{ AU}$</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5950,38 +5668,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ভীনের সরণ সূত্র ও নক্ষত্রের পৃষ্ঠ তাপমাত্রা (সমস্যা 45)</t>
+          <t>পর্যবেক্ষণমূলক জ্যোতির্ভৌতবিদ্যা, যুগল নক্ষত্র ও আপেক্ষিক মহাজাগতিক বিজ্ঞান (Astrophysics &amp; Binary Stars)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>[সমস্যা 45: ভীনের সরণ সূত্র ও নক্ষত্রের পৃষ্ঠ তাপমাত্রা]
-সূর্যের বিকিরণ বর্ণালীতে সর্বোচ্চ তীব্রতার তরঙ্গদৈর্ঘ্য $\lambda_{max} = 5000\text{ \AA}$। অন্য একটি নক্ষত্রের সর্বোচ্চ তীব্রতার তরঙ্গদৈর্ঘ্য $8000\text{ \AA}$ হলে নক্ষত্রটির পৃষ্ঠের তাপমাত্রা কত? (সূর্যের তাপমাত্রা $6000\text{ K}$)</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+মহাজাগতিক অণুতরঙ্গ পটভূমি বিকিরণের (CMBR) নিখুঁত কৃষ্ণবস্তু তাপমাত্রা $T = 2.7255\text{ K}$। ভীনের সরণ সূত্রানুযায়ী এর সর্বোচ্চ বিকিরণ তীব্রতার তরঙ্গদৈর্ঘ্য $\lambda_{\max}$ কত মিলিমিটার এবং এটি তাড়িতচৌম্বক বর্ণালীর কোন অংশে পড়ে?</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 45)।</t>
+          <t>ভীনের সূত্র: $\lambda_{\max} = \frac{b}{T} = \frac{2.898 \times 10^{-3}\text{ m}\cdot\text{K}}{2.7255\text{ K}} \approx 1.0633 \times 10^{-3}\text{ m} = 1.063\text{ mm}$। ১ মিলিমিটার তরঙ্গদৈর্ঘ্য নিখুঁতভাবে মাইক্রোওয়েভ অঞ্চলের অন্তর্ভুক্ত।</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 45</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+          <t>তরঙ্গদৈর্ঘ্য $\lambda_{\max} = 1.063\text{ mm}$ (মাইক্রোওয়েভ / অণুতরঙ্গ অঞ্চল)</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6001,12 +5719,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>স্টিফান-বোল্টজম্যান সূত্র ও নক্ষত্রের দীপ্তি (সমস্যা 46)</t>
+          <t>পর্যবেক্ষণমূলক জ্যোতির্ভৌতবিদ্যা, যুগল নক্ষত্র ও আপেক্ষিক মহাজাগতিক বিজ্ঞান (Astrophysics &amp; Binary Stars)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -6014,25 +5732,25 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>[সমস্যা 46: স্টিফান-বোল্টজম্যান সূত্র ও নক্ষত্রের দীপ্তি]
-একটি নক্ষত্রের ব্যাসার্ধ সূর্যের ব্যাসার্ধের দ্বিগুণ এবং পৃষ্ঠের তাপমাত্রা সূর্যের তাপমাত্রার 10 গুণ। নক্ষত্রটির সামগ্রিক দীপ্তি (Luminosity) সূর্যের তুলনায় কত গুণ হবে? ($L \propto R^2 T^4$)</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি যুগল তারা (Binary Star) ব্যবস্থার পর্যায়কাল $P = 20.0\text{ বছর}$ এবং তাদের মধ্যকার গড় কক্ষপথের অর্ধ-মুখ্য অক্ষ $a = 15.0\text{ AU}$। কেপলারের ৩য় সূত্রের নিউটনীয় রূপ $(M_1 + M_2) = \frac{a^3}{P^2}$ ব্যবহার করে যুগল ব্যবস্থার মোট ভর সৌর ভরে ($M_\odot$) নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 46)।</t>
+          <t>কেপলারের সংশোধিত ৩য় সূত্র: $\frac{a^3}{P^2} = \frac{G(M_1 + M_2)}{4\pi^2}$। সৌর একক ($a$ ইন $\text{AU}$, $P$ ইন বছর, ভর ইন $M_\odot$)-এ সমীকরণটি সরাসরি দাঁড়ায়: $M_{\text{total}} = \frac{a^3}{P^2} = \frac{15.0^3}{20.0^2} = \frac{3375}{400} = 8.4375 M_\odot \approx 8.44 M_\odot$।</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 46</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+          <t>মোট ভর $(M_1 + M_2) = 8.44 M_\odot$</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6052,38 +5770,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>চন্দ্রশেখর সীমা ও শ্বেত বামন নক্ষত্র (সমস্যা 47)</t>
+          <t>পর্যবেক্ষণমূলক জ্যোতির্ভৌতবিদ্যা, যুগল নক্ষত্র ও আপেক্ষিক মহাজাগতিক বিজ্ঞান (Astrophysics &amp; Binary Stars)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>[সমস্যা 47: চন্দ্রশেখর সীমা ও শ্বেত বামন নক্ষত্র]
-সূর্যের ভরের ১.৪ গুণ ভর ($1.4 M_\odot$) চন্দ্রশেখর সীমা নামে পরিচিত। $M = 12.0 M_\odot$ ভরের একটি নক্ষত্রের মৃত্যুর পর এর সম্ভাব্য রূপ কী হবে—শ্বেত বামন, নিউট্রন স্টার না ব্ল্যাকহোল?</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+কালপুরুষ তারামণ্ডলীর কালপুরুষ- $\alpha$ (Betelgeuse) একটি লোহিত দানব নক্ষত্র যার পৃষ্ঠ তাপমাত্রা $T = 3500.0\text{ K}$ এবং দীপ্তি সূর্যের এক লক্ষ গুণ ($L = 10^5 L_\odot$)। সূর্যের পৃষ্ঠ তাপমাত্রা $5800.0\text{ K}$ হলে আর্দ্রা নক্ষত্রের ব্যাসার্ধ সৌর ব্যাসার্ধের ($R_\odot$) কত গুণ এবং অ্যাস্ট্রোনমিক্যাল ইউনিটে ($	ext{AU}$) এর বিস্তার কত? ($1\text{ AU} pprox 215 R_\odot$)।</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 47)।</t>
+          <t>দীপ্তি অনুপাত: $\frac{L}{L_\odot} = \left(\frac{R}{R_\odot}\right)^2 \left(\frac{T}{T_\odot}\right)^4 \implies 10^5 = \left(\frac{R}{R_\odot}\right)^2 \left(\frac{3500}{5800}\right)^4 = \left(\frac{R}{R_\odot}\right)^2 (0.60345)^4 \approx \left(\frac{R}{R_\odot}\right)^2 \times 0.1326$। সুতরাং $\left(\frac{R}{R_\odot}\right)^2 = \frac{100000}{0.1326} \approx 754148 \implies \frac{R}{R_\odot} \approx \sqrt{754148} \approx 868.4$ গুণ। $\text{AU}$-তে: $R = \frac{868.4}{215} \approx 4.04\text{ AU}$।</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 47</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+          <t>ব্যাসার্ধ $R \approx 868.5 R_\odot \approx 4.04\text{ AU}$ (বৃহস্পতির কক্ষপথের সমান সুবিশাল আকার)</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6103,12 +5821,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>মহাবিশ্বের আনুমানিক বয়স নির্ণয় (সমস্যা 48)</t>
+          <t>পর্যবেক্ষণমূলক জ্যোতির্ভৌতবিদ্যা, যুগল নক্ষত্র ও আপেক্ষিক মহাজাগতিক বিজ্ঞান (Astrophysics &amp; Binary Stars)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -6116,25 +5834,25 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>[সমস্যা 48: মহাবিশ্বের আনুমানিক বয়স নির্ণয়]
-হাবল ধ্রুবক $H_0 = 20\text{ km/s/Mpc}$ হলে হাবল সময়ের সূত্রানুসারে ($t = 1/H_0$) আমাদের মহাবিশ্বের আনুমানিক বয়স কত বিলিয়ন বছর হবে?</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+আধুনিক মহাজাগতিক মডেলে পদার্থের ঘনত্ব প্যারামিটার $\Omega_m = 0.315$ এবং ডার্ক এনার্জির ঘনত্ব প্যারামিটার $\Omega_\Lambda = 0.685$ হলে মোট ঘনত্ব প্যারামিটার $\Omega_0$ কত? এটি মহাবিশ্বের জ্যামিতিক স্থানকালিক বক্রতা সম্পর্কে কী সিদ্ধান্ত দেয়?</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 48)।</t>
+          <t>মোট ঘনত্ব প্যারামিটার $\Omega_0 = \Omega_m + \Omega_\Lambda = 0.315 + 0.685 = 1.000$। ফ্রিডম্যানের সমীকরণ অনুসারে যদি $\Omega_0 = 1$ হয়, তবে স্থানকালের বৈশ্বিক জ্যামিতি ইউক্লিডীয় বা শূন্য বক্রতার সমতল ($k = 0$) হয়, যেখানে সমান্তরাল আলোকরশ্মি মহাজাগতিক দূরত্বেও কখনোই মিলিত বা অপসারিত হয় না।</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 48</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+          <t>মোট ঘনত্ব প্যারামিটার $\Omega_0 = 1.00$; মহাবিশ্ব স্থানকালিকভাবে নিখুঁত সমতল (Spatially Flat Universe, $k = 0$)</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6154,38 +5872,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>নক্ষত্রের লাল সরণ ও ডপলার প্রভাব (সমস্যা 49)</t>
+          <t>পর্যবেক্ষণমূলক জ্যোতির্ভৌতবিদ্যা, যুগল নক্ষত্র ও আপেক্ষিক মহাজাগতিক বিজ্ঞান (Astrophysics &amp; Binary Stars)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>[সমস্যা 49: নক্ষত্রের লাল সরণ ও ডপলার প্রভাব]
-একটি দূরবর্তী কোয়াসার হতে আগত হাইড্রোজেন $\text{H}_\alpha$ বর্ণালী রেখার প্রকৃত তরঙ্গদৈর্ঘ্য $6563\text{ \AA}$ কিন্তু পৃথিবীতে পরিমাপকৃত মান $4000\text{ \AA}$। কোয়াসারটির লাল সরণ ($z = \Delta\lambda / \lambda$) কত?</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+দুটি অভিন্ন দীপ্তির নক্ষত্র $A$ ও $B$-এর পরম মান সমান ($M_A = M_B$)। নক্ষত্র $A$-এর দূরত্ব $d_A = 10.0\text{ pc}$ এবং $B$-এর দূরত্ব $d_B = 50.0\text{ pc}$ হলে: (ক) পৃথিবীতে এদের আপাত বিকিরণ তীব্রতার অনুপাত $F_A / F_B$, এবং (খ) তাদের আপাত মানের পার্থক্য $m_B - m_A$ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 49)।</t>
+          <t>দূরত্বের বিপরীত বর্গীয় সূত্র: $F = \frac{L}{4\pi d^2} \implies \frac{F_A}{F_B} = \left(\frac{d_B}{d_A}\right)^2 = \left(\frac{50}{10}\right)^2 = 5^2 = 25.0$। আপাত মানের পার্থক্য: $m_B - m_A = 2.5\log_{10}\left(\frac{F_A}{F_B}\right) = 2.5\log_{10}(25) = 2.5 \times 1.39794 \approx 3.4948 \approx 3.49$ মান।</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 49</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+          <t>(ক) তীব্রতার অনুপাত $F_A / F_B = 25.0$, (খ) আপাত মানের পার্থক্য $m_B - m_A = 3.49$ মান</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6205,12 +5923,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>মহাজাগতিক পটভূমি বিকিরণ (CMBR) (সমস্যা 50)</t>
+          <t>পর্যবেক্ষণমূলক জ্যোতির্ভৌতবিদ্যা, যুগল নক্ষত্র ও আপেক্ষিক মহাজাগতিক বিজ্ঞান (Astrophysics &amp; Binary Stars)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -6218,25 +5936,25 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>[সমস্যা 50: মহাজাগতিক পটভূমি বিকিরণ (CMBR)]
-মহাজাগতিক পটভূমি বিকিরণের বর্তমান তাপমাত্রা $T = 2.76\text{ K}$। ভীনের সূত্র $\lambda_{max} T = 2.898 \times 10^{-3}\text{ m}\cdot\text{K}$ দ্বারা এই বিকিরণের শীর্ষ তরঙ্গদৈর্ঘ্য কোন অঞ্চলে পড়ে হিসাব কর।</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি নিউট্রন তারার ভর $M = 1.5 M_\odot = 3.0 \times 10^{30}\text{ kg}$ এবং ব্যাসার্ধ $R = 12.0\text{ km}$। এর পৃষ্ঠ হতে $\lambda_0 = 500.0\text{ nm}$ তরঙ্গদৈর্ঘ্যের আলো নিঃসৃত হলে সাধারণ আপেক্ষিকতার মহাকর্ষীয় রেডশিফট সূত্র $1 + z_g = \frac{1}{\sqrt{1 - \frac{2 G M}{R c^2}}}$ ব্যবহার করে অসীমে অবস্থিত পর্যবেক্ষক কর্তৃক পরিমাপকৃত তরঙ্গদৈর্ঘ্য $\lambda$ কত হবে?</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>হাবলের সূত্র, মহাকর্ষীয় সংকোচন ও সোয়ার্জশিল্ড সমীকরণ প্রয়োগ করে জ্যোতির্বৈজ্ঞানিক হিসাব (সমস্যা 50)।</t>
+          <t>সোয়ার্জশিল্ড ফ্যাক্টর: $\frac{2 G M}{R c^2} = \frac{2 \times (6.674 \times 10^{-11}) \times (3.0 \times 10^{30})}{(1.20 \times 10^4) \times (3.0 \times 10^8)^2} = \frac{4.0044 \times 10^{20}}{1.08 \times 10^{21}} \approx 0.37077$। রুট মান: $\sqrt{1 - 0.37077} = \sqrt{0.62923} \approx 0.7932$। অতএব $1 + z_g = \frac{1}{0.7932} \approx 1.2606 \implies \lambda = \lambda_0 (1 + z_g) = 500.0 \times 1.2606 \approx 630.3\text{ nm}$ (সবুজ আলো তীব্র মহাকর্ষীয় টানে লাল আলোতে রূপান্তরিত হয়)।</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>জ্যোতির্বিজ্ঞানের উত্তর 50</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+          <t>পর্যবেক্ষিত তরঙ্গদৈর্ঘ্য $\lambda = 650.0\text{ nm}$ ($z_g = 0.300$)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
